--- a/dist/Кафедра_ИС_занятия_преподавателей_2026-2027.xlsx
+++ b/dist/Кафедра_ИС_занятия_преподавателей_2026-2027.xlsx
@@ -1390,7 +1390,7 @@
       </c>
       <c r="G3" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H3" s="9" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H4" s="9" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H5" s="9" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H6" s="9" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H20" s="9" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="G51" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H51" s="9" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="G52" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H52" s="9" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="G53" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H53" s="9" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="G54" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H54" s="9" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="G55" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H55" s="9" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="G56" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H56" s="9" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="G57" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H57" s="9" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="G58" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H58" s="9" t="inlineStr">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="G59" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H59" s="9" t="inlineStr">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="G60" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H60" s="9" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="G62" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H62" s="9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="G63" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H63" s="9" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="G64" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H64" s="9" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="G65" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H65" s="9" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="G66" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H66" s="9" t="inlineStr">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="G67" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H67" s="9" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="G68" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H68" s="9" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="G69" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H69" s="9" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="G70" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H70" s="9" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="G71" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H71" s="9" t="inlineStr">
@@ -4288,7 +4288,7 @@
       </c>
       <c r="G72" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H72" s="9" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="G73" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H73" s="9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="G74" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H74" s="9" t="inlineStr">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="G75" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H75" s="9" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="G76" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H76" s="9" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="G77" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H77" s="9" t="inlineStr">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="G78" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H78" s="9" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="G79" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H79" s="9" t="inlineStr">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="G80" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H80" s="9" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="G81" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H81" s="9" t="inlineStr">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="G82" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H82" s="9" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="G83" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H83" s="9" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="G125" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H125" s="9" t="inlineStr">
@@ -6598,7 +6598,7 @@
       </c>
       <c r="G127" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H127" s="9" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="G130" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H130" s="9" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="G131" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H131" s="9" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="G135" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H135" s="9" t="inlineStr">
@@ -7060,7 +7060,7 @@
       </c>
       <c r="G138" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H138" s="9" t="inlineStr">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="G139" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H139" s="9" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="G141" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H141" s="9" t="inlineStr">
@@ -8483,7 +8483,7 @@
       </c>
       <c r="F172" s="8" t="inlineStr">
         <is>
-          <t>Компьютерные сети/Казангапова Б.А./лабораторная/404-С</t>
+          <t>Основы информационной безопасности/Казангапова Б.А./лабораторная/316-Б</t>
         </is>
       </c>
       <c r="G172" s="9" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="G180" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H180" s="9" t="inlineStr">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="G181" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H181" s="9" t="inlineStr">
@@ -8908,7 +8908,7 @@
       </c>
       <c r="G182" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H182" s="9" t="inlineStr">
@@ -8950,7 +8950,7 @@
       </c>
       <c r="G183" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H183" s="9" t="inlineStr">
@@ -8992,7 +8992,7 @@
       </c>
       <c r="G184" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H184" s="9" t="inlineStr">
@@ -9192,7 +9192,7 @@
       </c>
       <c r="E189" s="5" t="inlineStr">
         <is>
-          <t>6В06101-ИС-26-11 (30)</t>
+          <t>6В06101-ИС-26-11 ()</t>
         </is>
       </c>
       <c r="F189" s="8" t="inlineStr">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="G189" s="9" t="inlineStr">
         <is>
-          <t>1_курс_2026-2027_ФИТ_ФИиС_ФЭб_ФДТиО.xlsx</t>
+          <t>Г_Ж_1_курс_2026-2027_Фэб_фдтио_Фиит.xlsx</t>
         </is>
       </c>
       <c r="H189" s="9" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="E196" s="5" t="inlineStr">
         <is>
-          <t>6В06101-ИС-26-11 (30)</t>
+          <t>6В06101-ИС-26-11 ()</t>
         </is>
       </c>
       <c r="F196" s="8" t="inlineStr">
@@ -9496,7 +9496,7 @@
       </c>
       <c r="G196" s="9" t="inlineStr">
         <is>
-          <t>1_курс_2026-2027_ФИТ_ФИиС_ФЭб_ФДТиО.xlsx</t>
+          <t>Г_Ж_1_курс_2026-2027_Фэб_фдтио_Фиит.xlsx</t>
         </is>
       </c>
       <c r="H196" s="9" t="inlineStr">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="E197" s="5" t="inlineStr">
         <is>
-          <t>6В06101-ИС-26-12 (29)</t>
+          <t>6В06101-ИС-26-12 ()</t>
         </is>
       </c>
       <c r="F197" s="8" t="inlineStr">
@@ -9538,7 +9538,7 @@
       </c>
       <c r="G197" s="9" t="inlineStr">
         <is>
-          <t>1_курс_2026-2027_ФИТ_ФИиС_ФЭб_ФДТиО.xlsx</t>
+          <t>Г_Ж_1_курс_2026-2027_Фэб_фдтио_Фиит.xlsx</t>
         </is>
       </c>
       <c r="H197" s="9" t="inlineStr">
@@ -9738,7 +9738,7 @@
       </c>
       <c r="E202" s="5" t="inlineStr">
         <is>
-          <t>6В06101-ИС-26-14 (29)</t>
+          <t>6В06101-ИС-26-14 ()каз</t>
         </is>
       </c>
       <c r="F202" s="8" t="inlineStr">
@@ -9748,7 +9748,7 @@
       </c>
       <c r="G202" s="9" t="inlineStr">
         <is>
-          <t>1_курс_2026-2027_ФИТ_ФИиС_ФЭб_ФДТиО.xlsx</t>
+          <t>Г_Ж_1_курс_2026-2027_Фэб_фдтио_Фиит.xlsx</t>
         </is>
       </c>
       <c r="H202" s="9" t="inlineStr">
@@ -9822,7 +9822,7 @@
       </c>
       <c r="E204" s="5" t="inlineStr">
         <is>
-          <t>6В06101-ИС-26-14 (29)</t>
+          <t>6В06101-ИС-26-14 ()каз</t>
         </is>
       </c>
       <c r="F204" s="8" t="inlineStr">
@@ -9832,7 +9832,7 @@
       </c>
       <c r="G204" s="9" t="inlineStr">
         <is>
-          <t>1_курс_2026-2027_ФИТ_ФИиС_ФЭб_ФДТиО.xlsx</t>
+          <t>Г_Ж_1_курс_2026-2027_Фэб_фдтио_Фиит.xlsx</t>
         </is>
       </c>
       <c r="H204" s="9" t="inlineStr">
@@ -10032,7 +10032,7 @@
       </c>
       <c r="E209" s="5" t="inlineStr">
         <is>
-          <t>6В06101-ИС-26-13 (30)</t>
+          <t>6В06101-ИС-26-13 ()</t>
         </is>
       </c>
       <c r="F209" s="8" t="inlineStr">
@@ -10042,7 +10042,7 @@
       </c>
       <c r="G209" s="9" t="inlineStr">
         <is>
-          <t>1_курс_2026-2027_ФИТ_ФИиС_ФЭб_ФДТиО.xlsx</t>
+          <t>Г_Ж_1_курс_2026-2027_Фэб_фдтио_Фиит.xlsx</t>
         </is>
       </c>
       <c r="H209" s="9" t="inlineStr">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="E210" s="5" t="inlineStr">
         <is>
-          <t>6В06101-ИС-26-15 (21)</t>
+          <t>6В06101-ИС-26-15  )қаз</t>
         </is>
       </c>
       <c r="F210" s="8" t="inlineStr">
@@ -10084,7 +10084,7 @@
       </c>
       <c r="G210" s="9" t="inlineStr">
         <is>
-          <t>1_курс_2026-2027_ФИТ_ФИиС_ФЭб_ФДТиО.xlsx</t>
+          <t>Г_Ж_1_курс_2026-2027_Фэб_фдтио_Фиит.xlsx</t>
         </is>
       </c>
       <c r="H210" s="9" t="inlineStr">
@@ -10116,7 +10116,7 @@
       </c>
       <c r="E211" s="5" t="inlineStr">
         <is>
-          <t>ИС-26-16 (21)</t>
+          <t>ИС-26-16 ()қаз</t>
         </is>
       </c>
       <c r="F211" s="8" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="G211" s="9" t="inlineStr">
         <is>
-          <t>1_курс_2026-2027_ФИТ_ФИиС_ФЭб_ФДТиО.xlsx</t>
+          <t>Г_Ж_1_курс_2026-2027_Фэб_фдтио_Фиит.xlsx</t>
         </is>
       </c>
       <c r="H211" s="9" t="inlineStr">
@@ -11508,7 +11508,7 @@
       </c>
       <c r="G244" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H244" s="9" t="inlineStr">
@@ -11550,7 +11550,7 @@
       </c>
       <c r="G245" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H245" s="9" t="inlineStr">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="G288" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H288" s="9" t="inlineStr">
@@ -13398,7 +13398,7 @@
       </c>
       <c r="G289" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H289" s="9" t="inlineStr">
@@ -13440,7 +13440,7 @@
       </c>
       <c r="G290" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H290" s="9" t="inlineStr">
@@ -13482,7 +13482,7 @@
       </c>
       <c r="G291" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H291" s="9" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="G292" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H292" s="9" t="inlineStr">
@@ -13566,7 +13566,7 @@
       </c>
       <c r="G293" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H293" s="9" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="G332" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H332" s="9" t="inlineStr">
@@ -16296,7 +16296,7 @@
       </c>
       <c r="G358" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H358" s="9" t="inlineStr">
@@ -16338,7 +16338,7 @@
       </c>
       <c r="G359" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H359" s="9" t="inlineStr">
@@ -16380,7 +16380,7 @@
       </c>
       <c r="G360" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H360" s="9" t="inlineStr">
@@ -16422,7 +16422,7 @@
       </c>
       <c r="G361" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H361" s="9" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="G362" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H362" s="9" t="inlineStr">
@@ -16506,7 +16506,7 @@
       </c>
       <c r="G363" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H363" s="9" t="inlineStr">
@@ -16548,7 +16548,7 @@
       </c>
       <c r="G364" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H364" s="9" t="inlineStr">
@@ -16590,7 +16590,7 @@
       </c>
       <c r="G365" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H365" s="9" t="inlineStr">
@@ -16632,7 +16632,7 @@
       </c>
       <c r="G366" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H366" s="9" t="inlineStr">
@@ -16758,7 +16758,7 @@
       </c>
       <c r="G369" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H369" s="9" t="inlineStr">
@@ -16842,7 +16842,7 @@
       </c>
       <c r="G371" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H371" s="9" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="G372" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H372" s="9" t="inlineStr">
@@ -16968,7 +16968,7 @@
       </c>
       <c r="G374" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H374" s="9" t="inlineStr">
@@ -17010,7 +17010,7 @@
       </c>
       <c r="G375" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H375" s="9" t="inlineStr">
@@ -17052,7 +17052,7 @@
       </c>
       <c r="G376" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H376" s="9" t="inlineStr">
@@ -17262,7 +17262,7 @@
       </c>
       <c r="G381" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H381" s="9" t="inlineStr">
@@ -17388,7 +17388,7 @@
       </c>
       <c r="G384" s="9" t="inlineStr">
         <is>
-          <t>1_курс_2026-2027_ФИТ_ФИиС_ФЭб_ФДТиО.xlsx</t>
+          <t>Г_Ж_1_курс_2026-2027_Фэб_фдтио_Фиит.xlsx</t>
         </is>
       </c>
       <c r="H384" s="9" t="inlineStr">
@@ -17472,7 +17472,7 @@
       </c>
       <c r="G386" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H386" s="9" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="G387" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H387" s="9" t="inlineStr">
@@ -17556,7 +17556,7 @@
       </c>
       <c r="G388" s="9" t="inlineStr">
         <is>
-          <t>1_курс_2026-2027_ФИТ_ФИиС_ФЭб_ФДТиО.xlsx</t>
+          <t>Г_Ж_1_курс_2026-2027_Фэб_фдтио_Фиит.xlsx</t>
         </is>
       </c>
       <c r="H388" s="9" t="inlineStr">
@@ -17766,7 +17766,7 @@
       </c>
       <c r="G393" s="9" t="inlineStr">
         <is>
-          <t>1_курс_2026-2027_ФИТ_ФИиС_ФЭб_ФДТиО.xlsx</t>
+          <t>Г_Ж_1_курс_2026-2027_Фэб_фдтио_Фиит.xlsx</t>
         </is>
       </c>
       <c r="H393" s="9" t="inlineStr">
@@ -18018,7 +18018,7 @@
       </c>
       <c r="G399" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H399" s="9" t="inlineStr">
@@ -18102,7 +18102,7 @@
       </c>
       <c r="G401" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H401" s="9" t="inlineStr">
@@ -18816,7 +18816,7 @@
       </c>
       <c r="G418" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H418" s="9" t="inlineStr">
@@ -18858,7 +18858,7 @@
       </c>
       <c r="G419" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H419" s="9" t="inlineStr">
@@ -19858,7 +19858,7 @@
       </c>
       <c r="G443" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H443" s="9" t="inlineStr">
@@ -19900,7 +19900,7 @@
       </c>
       <c r="G444" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
       <c r="H444" s="9" t="inlineStr">
@@ -20392,7 +20392,7 @@
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>Компьютерные сети/Казангапова Б.А./лабораторная/404-С</t>
+          <t>Основы информационной безопасности/Казангапова Б.А./лабораторная/316-Б</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
@@ -21281,7 +21281,7 @@
       </c>
       <c r="F54" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -21313,7 +21313,7 @@
       </c>
       <c r="F55" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -21345,7 +21345,7 @@
       </c>
       <c r="F56" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -21377,7 +21377,7 @@
       </c>
       <c r="F57" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -21409,7 +21409,7 @@
       </c>
       <c r="F58" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -21441,7 +21441,7 @@
       </c>
       <c r="F59" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -21473,7 +21473,7 @@
       </c>
       <c r="F60" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -21505,7 +21505,7 @@
       </c>
       <c r="F61" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -21537,7 +21537,7 @@
       </c>
       <c r="F62" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -21569,7 +21569,7 @@
       </c>
       <c r="F63" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -21633,7 +21633,7 @@
       </c>
       <c r="F65" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -21665,7 +21665,7 @@
       </c>
       <c r="F66" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -21697,7 +21697,7 @@
       </c>
       <c r="F67" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -21729,7 +21729,7 @@
       </c>
       <c r="F68" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -21761,7 +21761,7 @@
       </c>
       <c r="F69" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -21793,7 +21793,7 @@
       </c>
       <c r="F70" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -21864,7 +21864,7 @@
       </c>
       <c r="F74" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -21896,7 +21896,7 @@
       </c>
       <c r="F75" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -21928,7 +21928,7 @@
       </c>
       <c r="F76" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -21960,7 +21960,7 @@
       </c>
       <c r="F77" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -21992,7 +21992,7 @@
       </c>
       <c r="F78" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -22024,7 +22024,7 @@
       </c>
       <c r="F79" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -22056,7 +22056,7 @@
       </c>
       <c r="F80" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -22088,7 +22088,7 @@
       </c>
       <c r="F81" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -22120,7 +22120,7 @@
       </c>
       <c r="F82" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -22152,7 +22152,7 @@
       </c>
       <c r="F83" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -22184,7 +22184,7 @@
       </c>
       <c r="F84" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -22216,7 +22216,7 @@
       </c>
       <c r="F85" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -22248,7 +22248,7 @@
       </c>
       <c r="F86" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -22280,7 +22280,7 @@
       </c>
       <c r="F87" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -22312,7 +22312,7 @@
       </c>
       <c r="F88" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -22344,7 +22344,7 @@
       </c>
       <c r="F89" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -23212,7 +23212,7 @@
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>6В06101-ИС-26-11 (30)</t>
+          <t>6В06101-ИС-26-11 ()</t>
         </is>
       </c>
       <c r="E120" s="8" t="inlineStr">
@@ -23222,7 +23222,7 @@
       </c>
       <c r="F120" s="9" t="inlineStr">
         <is>
-          <t>1_курс_2026-2027_ФИТ_ФИиС_ФЭб_ФДТиО.xlsx</t>
+          <t>Г_Ж_1_курс_2026-2027_Фэб_фдтио_Фиит.xlsx</t>
         </is>
       </c>
     </row>
@@ -23436,7 +23436,7 @@
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>6В06101-ИС-26-11 (30)</t>
+          <t>6В06101-ИС-26-11 ()</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
@@ -23446,7 +23446,7 @@
       </c>
       <c r="F127" s="9" t="inlineStr">
         <is>
-          <t>1_курс_2026-2027_ФИТ_ФИиС_ФЭб_ФДТиО.xlsx</t>
+          <t>Г_Ж_1_курс_2026-2027_Фэб_фдтио_Фиит.xlsx</t>
         </is>
       </c>
     </row>
@@ -23468,7 +23468,7 @@
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>6В06101-ИС-26-12 (29)</t>
+          <t>6В06101-ИС-26-12 ()</t>
         </is>
       </c>
       <c r="E128" s="8" t="inlineStr">
@@ -23478,7 +23478,7 @@
       </c>
       <c r="F128" s="9" t="inlineStr">
         <is>
-          <t>1_курс_2026-2027_ФИТ_ФИиС_ФЭб_ФДТиО.xlsx</t>
+          <t>Г_Ж_1_курс_2026-2027_Фэб_фдтио_Фиит.xlsx</t>
         </is>
       </c>
     </row>
@@ -23628,7 +23628,7 @@
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>6В06101-ИС-26-14 (29)</t>
+          <t>6В06101-ИС-26-14 ()каз</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
@@ -23638,7 +23638,7 @@
       </c>
       <c r="F133" s="9" t="inlineStr">
         <is>
-          <t>1_курс_2026-2027_ФИТ_ФИиС_ФЭб_ФДТиО.xlsx</t>
+          <t>Г_Ж_1_курс_2026-2027_Фэб_фдтио_Фиит.xlsx</t>
         </is>
       </c>
     </row>
@@ -23692,7 +23692,7 @@
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>6В06101-ИС-26-14 (29)</t>
+          <t>6В06101-ИС-26-14 ()каз</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
@@ -23702,7 +23702,7 @@
       </c>
       <c r="F135" s="9" t="inlineStr">
         <is>
-          <t>1_курс_2026-2027_ФИТ_ФИиС_ФЭб_ФДТиО.xlsx</t>
+          <t>Г_Ж_1_курс_2026-2027_Фэб_фдтио_Фиит.xlsx</t>
         </is>
       </c>
     </row>
@@ -23852,7 +23852,7 @@
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>6В06101-ИС-26-13 (30)</t>
+          <t>6В06101-ИС-26-13 ()</t>
         </is>
       </c>
       <c r="E140" s="8" t="inlineStr">
@@ -23862,7 +23862,7 @@
       </c>
       <c r="F140" s="9" t="inlineStr">
         <is>
-          <t>1_курс_2026-2027_ФИТ_ФИиС_ФЭб_ФДТиО.xlsx</t>
+          <t>Г_Ж_1_курс_2026-2027_Фэб_фдтио_Фиит.xlsx</t>
         </is>
       </c>
     </row>
@@ -23884,7 +23884,7 @@
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>6В06101-ИС-26-15 (21)</t>
+          <t>6В06101-ИС-26-15  )қаз</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
@@ -23894,7 +23894,7 @@
       </c>
       <c r="F141" s="9" t="inlineStr">
         <is>
-          <t>1_курс_2026-2027_ФИТ_ФИиС_ФЭб_ФДТиО.xlsx</t>
+          <t>Г_Ж_1_курс_2026-2027_Фэб_фдтио_Фиит.xlsx</t>
         </is>
       </c>
     </row>
@@ -23916,7 +23916,7 @@
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>ИС-26-16 (21)</t>
+          <t>ИС-26-16 ()қаз</t>
         </is>
       </c>
       <c r="E142" s="8" t="inlineStr">
@@ -23926,7 +23926,7 @@
       </c>
       <c r="F142" s="9" t="inlineStr">
         <is>
-          <t>1_курс_2026-2027_ФИТ_ФИиС_ФЭб_ФДТиО.xlsx</t>
+          <t>Г_Ж_1_курс_2026-2027_Фэб_фдтио_Фиит.xlsx</t>
         </is>
       </c>
     </row>
@@ -24512,7 +24512,7 @@
       </c>
       <c r="F164" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -24576,7 +24576,7 @@
       </c>
       <c r="F166" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -24608,7 +24608,7 @@
       </c>
       <c r="F167" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -24672,7 +24672,7 @@
       </c>
       <c r="F169" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -24704,7 +24704,7 @@
       </c>
       <c r="F170" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -24736,7 +24736,7 @@
       </c>
       <c r="F171" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -24896,7 +24896,7 @@
       </c>
       <c r="F176" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -24967,7 +24967,7 @@
       </c>
       <c r="F180" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -24999,7 +24999,7 @@
       </c>
       <c r="F181" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -25031,7 +25031,7 @@
       </c>
       <c r="F182" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -25063,7 +25063,7 @@
       </c>
       <c r="F183" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -25095,7 +25095,7 @@
       </c>
       <c r="F184" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -25813,7 +25813,7 @@
       </c>
       <c r="F210" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -25877,7 +25877,7 @@
       </c>
       <c r="F212" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -26421,7 +26421,7 @@
       </c>
       <c r="F229" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -26453,7 +26453,7 @@
       </c>
       <c r="F230" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -29983,7 +29983,7 @@
       </c>
       <c r="F351" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -30015,7 +30015,7 @@
       </c>
       <c r="F352" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -30047,7 +30047,7 @@
       </c>
       <c r="F353" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -30079,7 +30079,7 @@
       </c>
       <c r="F354" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -30111,7 +30111,7 @@
       </c>
       <c r="F355" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -30143,7 +30143,7 @@
       </c>
       <c r="F356" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -30797,7 +30797,7 @@
       </c>
       <c r="F380" s="9" t="inlineStr">
         <is>
-          <t>1_курс_2026-2027_ФИТ_ФИиС_ФЭб_ФДТиО.xlsx</t>
+          <t>Г_Ж_1_курс_2026-2027_Фэб_фдтио_Фиит.xlsx</t>
         </is>
       </c>
     </row>
@@ -30861,7 +30861,7 @@
       </c>
       <c r="F382" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -30893,7 +30893,7 @@
       </c>
       <c r="F383" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -30925,7 +30925,7 @@
       </c>
       <c r="F384" s="9" t="inlineStr">
         <is>
-          <t>1_курс_2026-2027_ФИТ_ФИиС_ФЭб_ФДТиО.xlsx</t>
+          <t>Г_Ж_1_курс_2026-2027_Фэб_фдтио_Фиит.xlsx</t>
         </is>
       </c>
     </row>
@@ -31085,7 +31085,7 @@
       </c>
       <c r="F389" s="9" t="inlineStr">
         <is>
-          <t>1_курс_2026-2027_ФИТ_ФИиС_ФЭб_ФДТиО.xlsx</t>
+          <t>Г_Ж_1_курс_2026-2027_Фэб_фдтио_Фиит.xlsx</t>
         </is>
       </c>
     </row>
@@ -32059,7 +32059,7 @@
       </c>
       <c r="F423" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -32123,7 +32123,7 @@
       </c>
       <c r="F425" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -32219,7 +32219,7 @@
       </c>
       <c r="F428" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -32251,7 +32251,7 @@
       </c>
       <c r="F429" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -32379,7 +32379,7 @@
       </c>
       <c r="F433" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -33328,7 +33328,7 @@
       </c>
       <c r="F468" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -33360,7 +33360,7 @@
       </c>
       <c r="F469" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -33392,7 +33392,7 @@
       </c>
       <c r="F470" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -33424,7 +33424,7 @@
       </c>
       <c r="F471" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -33456,7 +33456,7 @@
       </c>
       <c r="F472" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -33488,7 +33488,7 @@
       </c>
       <c r="F473" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -33520,7 +33520,7 @@
       </c>
       <c r="F474" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -33552,7 +33552,7 @@
       </c>
       <c r="F475" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -33584,7 +33584,7 @@
       </c>
       <c r="F476" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -34163,7 +34163,7 @@
       </c>
       <c r="F503" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -34195,7 +34195,7 @@
       </c>
       <c r="F504" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -34227,7 +34227,7 @@
       </c>
       <c r="F505" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -34259,7 +34259,7 @@
       </c>
       <c r="F506" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -34291,7 +34291,7 @@
       </c>
       <c r="F507" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -34724,7 +34724,7 @@
       </c>
       <c r="F533" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -34962,7 +34962,7 @@
       </c>
       <c r="F544" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -34994,7 +34994,7 @@
       </c>
       <c r="F545" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -35026,7 +35026,7 @@
       </c>
       <c r="F546" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -35058,7 +35058,7 @@
       </c>
       <c r="F547" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -35129,7 +35129,7 @@
       </c>
       <c r="F551" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -35161,7 +35161,7 @@
       </c>
       <c r="F552" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -35264,7 +35264,7 @@
       </c>
       <c r="F557" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -35296,7 +35296,7 @@
       </c>
       <c r="F558" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -35367,7 +35367,7 @@
       </c>
       <c r="F562" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -35399,7 +35399,7 @@
       </c>
       <c r="F563" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>
@@ -35463,7 +35463,7 @@
       </c>
       <c r="F565" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_09_09.xlsx</t>
+          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
         </is>
       </c>
     </row>

--- a/dist/Кафедра_ИС_занятия_преподавателей_2026-2027.xlsx
+++ b/dist/Кафедра_ИС_занятия_преподавателей_2026-2027.xlsx
@@ -1348,7 +1348,7 @@
       </c>
       <c r="G2" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H2" s="9" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="G3" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H3" s="9" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H4" s="9" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H5" s="9" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H6" s="9" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H7" s="9" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H8" s="9" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H9" s="9" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H11" s="9" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H20" s="9" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H25" s="9" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H26" s="9" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H27" s="9" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H28" s="9" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H29" s="9" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>Расписание_магистрантов_2_курс.xlsx</t>
+          <t>magistratura_2kurs.xlsx</t>
         </is>
       </c>
       <c r="H30" s="9" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
-          <t>Расписание_магистрантов_2_курс.xlsx</t>
+          <t>magistratura_2kurs.xlsx</t>
         </is>
       </c>
       <c r="H31" s="9" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>МАГИСТРАТУРА_1_КУРС_ПРОФИЛЬНОЕ_НАПР__2026-2027_г_.xlsx</t>
+          <t>magistratura_profil.xlsx</t>
         </is>
       </c>
       <c r="H32" s="9" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H33" s="9" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H34" s="9" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H35" s="9" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H36" s="9" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="G37" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H37" s="9" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="G38" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H38" s="9" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="G39" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H39" s="9" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="G40" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H40" s="9" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="G41" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H41" s="9" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="G42" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H42" s="9" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="G43" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H43" s="9" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="G44" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H44" s="9" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="G45" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H45" s="9" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="G46" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H46" s="9" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="G47" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H47" s="9" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="G48" s="9" t="inlineStr">
         <is>
-          <t>Расписание_магистрантов_2_курс.xlsx</t>
+          <t>magistratura_2kurs.xlsx</t>
         </is>
       </c>
       <c r="H48" s="9" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="G49" s="9" t="inlineStr">
         <is>
-          <t>Расписание_магистрантов_2_курс.xlsx</t>
+          <t>magistratura_2kurs.xlsx</t>
         </is>
       </c>
       <c r="H49" s="9" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="G50" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H50" s="9" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="G51" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H51" s="9" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="G52" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H52" s="9" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="G53" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H53" s="9" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="G54" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H54" s="9" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="G55" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H55" s="9" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="G56" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H56" s="9" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="G57" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H57" s="9" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="G58" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H58" s="9" t="inlineStr">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="G59" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H59" s="9" t="inlineStr">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="G60" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H60" s="9" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="G61" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H61" s="9" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="G62" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H62" s="9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="G63" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H63" s="9" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="G64" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H64" s="9" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="G65" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H65" s="9" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="G66" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H66" s="9" t="inlineStr">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="G67" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H67" s="9" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="G68" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H68" s="9" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="G69" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H69" s="9" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="G70" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H70" s="9" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="G71" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H71" s="9" t="inlineStr">
@@ -4288,7 +4288,7 @@
       </c>
       <c r="G72" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H72" s="9" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="G73" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H73" s="9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="G74" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H74" s="9" t="inlineStr">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="G75" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H75" s="9" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="G76" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H76" s="9" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="G77" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H77" s="9" t="inlineStr">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="G78" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H78" s="9" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="G79" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H79" s="9" t="inlineStr">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="G80" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H80" s="9" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="G81" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H81" s="9" t="inlineStr">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="G82" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H82" s="9" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="G83" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H83" s="9" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="G84" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H84" s="9" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="G85" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H85" s="9" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="G86" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H86" s="9" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="G87" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H87" s="9" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="G88" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H88" s="9" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="G89" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H89" s="9" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="G90" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H90" s="9" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="G91" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H91" s="9" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="G92" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H92" s="9" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="G93" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H93" s="9" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="G94" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H94" s="9" t="inlineStr">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="G95" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H95" s="9" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="G96" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H96" s="9" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="G97" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H97" s="9" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="G98" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H98" s="9" t="inlineStr">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="G99" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H99" s="9" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="G100" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H100" s="9" t="inlineStr">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="G101" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H101" s="9" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="G102" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H102" s="9" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="G103" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H103" s="9" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="G104" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H104" s="9" t="inlineStr">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="G105" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H105" s="9" t="inlineStr">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="G106" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H106" s="9" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="G107" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H107" s="9" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="G108" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H108" s="9" t="inlineStr">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="G109" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H109" s="9" t="inlineStr">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="G110" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H110" s="9" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="G111" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H111" s="9" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="G112" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H112" s="9" t="inlineStr">
@@ -6010,7 +6010,7 @@
       </c>
       <c r="G113" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H113" s="9" t="inlineStr">
@@ -6052,7 +6052,7 @@
       </c>
       <c r="G114" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H114" s="9" t="inlineStr">
@@ -6094,7 +6094,7 @@
       </c>
       <c r="G115" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H115" s="9" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="G116" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H116" s="9" t="inlineStr">
@@ -6178,7 +6178,7 @@
       </c>
       <c r="G117" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H117" s="9" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="G118" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H118" s="9" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="G119" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H119" s="9" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="G120" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H120" s="9" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="G121" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H121" s="9" t="inlineStr">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="G122" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H122" s="9" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="G123" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H123" s="9" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="G124" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H124" s="9" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="G125" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H125" s="9" t="inlineStr">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="G126" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H126" s="9" t="inlineStr">
@@ -6598,7 +6598,7 @@
       </c>
       <c r="G127" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H127" s="9" t="inlineStr">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="G128" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H128" s="9" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="G129" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H129" s="9" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="G130" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H130" s="9" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="G131" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H131" s="9" t="inlineStr">
@@ -6808,7 +6808,7 @@
       </c>
       <c r="G132" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H132" s="9" t="inlineStr">
@@ -6850,7 +6850,7 @@
       </c>
       <c r="G133" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H133" s="9" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="G134" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H134" s="9" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="G135" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H135" s="9" t="inlineStr">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="G136" s="9" t="inlineStr">
         <is>
-          <t>МАГИСТРАТУРА_1_КУРС_ПРОФИЛЬНОЕ_НАПР__2026-2027_г_.xlsx</t>
+          <t>magistratura_profil.xlsx</t>
         </is>
       </c>
       <c r="H136" s="9" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="G137" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H137" s="9" t="inlineStr">
@@ -7060,7 +7060,7 @@
       </c>
       <c r="G138" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H138" s="9" t="inlineStr">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="G139" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H139" s="9" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="G140" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H140" s="9" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="G141" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H141" s="9" t="inlineStr">
@@ -7228,7 +7228,7 @@
       </c>
       <c r="G142" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H142" s="9" t="inlineStr">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="G143" s="9" t="inlineStr">
         <is>
-          <t>Расписание_магистрантов_2_курс.xlsx</t>
+          <t>magistratura_2kurs.xlsx</t>
         </is>
       </c>
       <c r="H143" s="9" t="inlineStr">
@@ -7312,7 +7312,7 @@
       </c>
       <c r="G144" s="9" t="inlineStr">
         <is>
-          <t>Расписание_магистрантов_2_курс.xlsx</t>
+          <t>magistratura_2kurs.xlsx</t>
         </is>
       </c>
       <c r="H144" s="9" t="inlineStr">
@@ -7354,7 +7354,7 @@
       </c>
       <c r="G145" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H145" s="9" t="inlineStr">
@@ -7396,7 +7396,7 @@
       </c>
       <c r="G146" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H146" s="9" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="G147" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H147" s="9" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="G148" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H148" s="9" t="inlineStr">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="G149" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H149" s="9" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="G150" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H150" s="9" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="G151" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H151" s="9" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="G152" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H152" s="9" t="inlineStr">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="G153" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H153" s="9" t="inlineStr">
@@ -7732,7 +7732,7 @@
       </c>
       <c r="G154" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H154" s="9" t="inlineStr">
@@ -7774,7 +7774,7 @@
       </c>
       <c r="G155" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H155" s="9" t="inlineStr">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="G156" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H156" s="9" t="inlineStr">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="G157" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H157" s="9" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="G158" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H158" s="9" t="inlineStr">
@@ -7942,7 +7942,7 @@
       </c>
       <c r="G159" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H159" s="9" t="inlineStr">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="G160" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H160" s="9" t="inlineStr">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="G161" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H161" s="9" t="inlineStr">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="G162" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H162" s="9" t="inlineStr">
@@ -8110,7 +8110,7 @@
       </c>
       <c r="G163" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H163" s="9" t="inlineStr">
@@ -8152,7 +8152,7 @@
       </c>
       <c r="G164" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H164" s="9" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="G165" s="9" t="inlineStr">
         <is>
-          <t>Расписание_магистрантов_1_КУРС_НАУЧНО-ПЕД__НАПРАВЛЕНИЕ__2026-2027_уч_г_.xlsx</t>
+          <t>magistratura_nauchped.xlsx</t>
         </is>
       </c>
       <c r="H165" s="9" t="inlineStr">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="G166" s="9" t="inlineStr">
         <is>
-          <t>Расписание_магистрантов_1_КУРС_НАУЧНО-ПЕД__НАПРАВЛЕНИЕ__2026-2027_уч_г_.xlsx</t>
+          <t>magistratura_nauchped.xlsx</t>
         </is>
       </c>
       <c r="H166" s="9" t="inlineStr">
@@ -8278,7 +8278,7 @@
       </c>
       <c r="G167" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H167" s="9" t="inlineStr">
@@ -8320,7 +8320,7 @@
       </c>
       <c r="G168" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H168" s="9" t="inlineStr">
@@ -8362,7 +8362,7 @@
       </c>
       <c r="G169" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H169" s="9" t="inlineStr">
@@ -8404,7 +8404,7 @@
       </c>
       <c r="G170" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H170" s="9" t="inlineStr">
@@ -8446,7 +8446,7 @@
       </c>
       <c r="G171" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H171" s="9" t="inlineStr">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="G172" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H172" s="9" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="G173" s="9" t="inlineStr">
         <is>
-          <t>МАГИСТРАТУРА_1_КУРС_ПРОФИЛЬНОЕ_НАПР__2026-2027_г_.xlsx</t>
+          <t>magistratura_profil.xlsx</t>
         </is>
       </c>
       <c r="H173" s="9" t="inlineStr">
@@ -8572,7 +8572,7 @@
       </c>
       <c r="G174" s="9" t="inlineStr">
         <is>
-          <t>МАГИСТРАТУРА_1_КУРС_ПРОФИЛЬНОЕ_НАПР__2026-2027_г_.xlsx</t>
+          <t>magistratura_profil.xlsx</t>
         </is>
       </c>
       <c r="H174" s="9" t="inlineStr">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="G175" s="9" t="inlineStr">
         <is>
-          <t>Расписание_магистрантов_1_КУРС_НАУЧНО-ПЕД__НАПРАВЛЕНИЕ__2026-2027_уч_г_.xlsx</t>
+          <t>magistratura_nauchped.xlsx</t>
         </is>
       </c>
       <c r="H175" s="9" t="inlineStr">
@@ -8656,7 +8656,7 @@
       </c>
       <c r="G176" s="9" t="inlineStr">
         <is>
-          <t>Расписание_магистрантов_1_КУРС_НАУЧНО-ПЕД__НАПРАВЛЕНИЕ__2026-2027_уч_г_.xlsx</t>
+          <t>magistratura_nauchped.xlsx</t>
         </is>
       </c>
       <c r="H176" s="9" t="inlineStr">
@@ -8698,7 +8698,7 @@
       </c>
       <c r="G177" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H177" s="9" t="inlineStr">
@@ -8740,7 +8740,7 @@
       </c>
       <c r="G178" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H178" s="9" t="inlineStr">
@@ -8782,7 +8782,7 @@
       </c>
       <c r="G179" s="9" t="inlineStr">
         <is>
-          <t>МАГИСТРАТУРА_1_КУРС_ПРОФИЛЬНОЕ_НАПР__2026-2027_г_.xlsx</t>
+          <t>magistratura_profil.xlsx</t>
         </is>
       </c>
       <c r="H179" s="9" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="G180" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H180" s="9" t="inlineStr">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="G181" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H181" s="9" t="inlineStr">
@@ -8908,7 +8908,7 @@
       </c>
       <c r="G182" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H182" s="9" t="inlineStr">
@@ -8950,7 +8950,7 @@
       </c>
       <c r="G183" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H183" s="9" t="inlineStr">
@@ -8992,7 +8992,7 @@
       </c>
       <c r="G184" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H184" s="9" t="inlineStr">
@@ -9034,7 +9034,7 @@
       </c>
       <c r="G185" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H185" s="9" t="inlineStr">
@@ -9076,7 +9076,7 @@
       </c>
       <c r="G186" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H186" s="9" t="inlineStr">
@@ -9118,7 +9118,7 @@
       </c>
       <c r="G187" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H187" s="9" t="inlineStr">
@@ -9160,7 +9160,7 @@
       </c>
       <c r="G188" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H188" s="9" t="inlineStr">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="G189" s="9" t="inlineStr">
         <is>
-          <t>Г_Ж_1_курс_2026-2027_Фэб_фдтио_Фиит.xlsx</t>
+          <t>1_kurs.xlsx</t>
         </is>
       </c>
       <c r="H189" s="9" t="inlineStr">
@@ -9244,7 +9244,7 @@
       </c>
       <c r="G190" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H190" s="9" t="inlineStr">
@@ -9286,7 +9286,7 @@
       </c>
       <c r="G191" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H191" s="9" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="G192" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H192" s="9" t="inlineStr">
@@ -9370,7 +9370,7 @@
       </c>
       <c r="G193" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H193" s="9" t="inlineStr">
@@ -9412,7 +9412,7 @@
       </c>
       <c r="G194" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H194" s="9" t="inlineStr">
@@ -9454,7 +9454,7 @@
       </c>
       <c r="G195" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H195" s="9" t="inlineStr">
@@ -9496,7 +9496,7 @@
       </c>
       <c r="G196" s="9" t="inlineStr">
         <is>
-          <t>Г_Ж_1_курс_2026-2027_Фэб_фдтио_Фиит.xlsx</t>
+          <t>1_kurs.xlsx</t>
         </is>
       </c>
       <c r="H196" s="9" t="inlineStr">
@@ -9538,7 +9538,7 @@
       </c>
       <c r="G197" s="9" t="inlineStr">
         <is>
-          <t>Г_Ж_1_курс_2026-2027_Фэб_фдтио_Фиит.xlsx</t>
+          <t>1_kurs.xlsx</t>
         </is>
       </c>
       <c r="H197" s="9" t="inlineStr">
@@ -9580,7 +9580,7 @@
       </c>
       <c r="G198" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H198" s="9" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="G199" s="9" t="inlineStr">
         <is>
-          <t>Расписание_магистрантов_2_курс.xlsx</t>
+          <t>magistratura_2kurs.xlsx</t>
         </is>
       </c>
       <c r="H199" s="9" t="inlineStr">
@@ -9664,7 +9664,7 @@
       </c>
       <c r="G200" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H200" s="9" t="inlineStr">
@@ -9706,7 +9706,7 @@
       </c>
       <c r="G201" s="9" t="inlineStr">
         <is>
-          <t>Расписание_магистрантов_2_курс.xlsx</t>
+          <t>magistratura_2kurs.xlsx</t>
         </is>
       </c>
       <c r="H201" s="9" t="inlineStr">
@@ -9748,7 +9748,7 @@
       </c>
       <c r="G202" s="9" t="inlineStr">
         <is>
-          <t>Г_Ж_1_курс_2026-2027_Фэб_фдтио_Фиит.xlsx</t>
+          <t>1_kurs.xlsx</t>
         </is>
       </c>
       <c r="H202" s="9" t="inlineStr">
@@ -9790,7 +9790,7 @@
       </c>
       <c r="G203" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H203" s="9" t="inlineStr">
@@ -9832,7 +9832,7 @@
       </c>
       <c r="G204" s="9" t="inlineStr">
         <is>
-          <t>Г_Ж_1_курс_2026-2027_Фэб_фдтио_Фиит.xlsx</t>
+          <t>1_kurs.xlsx</t>
         </is>
       </c>
       <c r="H204" s="9" t="inlineStr">
@@ -9874,7 +9874,7 @@
       </c>
       <c r="G205" s="9" t="inlineStr">
         <is>
-          <t>Расписание_магистрантов_2_курс.xlsx</t>
+          <t>magistratura_2kurs.xlsx</t>
         </is>
       </c>
       <c r="H205" s="9" t="inlineStr">
@@ -9916,7 +9916,7 @@
       </c>
       <c r="G206" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H206" s="9" t="inlineStr">
@@ -9958,7 +9958,7 @@
       </c>
       <c r="G207" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H207" s="9" t="inlineStr">
@@ -10000,7 +10000,7 @@
       </c>
       <c r="G208" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H208" s="9" t="inlineStr">
@@ -10042,7 +10042,7 @@
       </c>
       <c r="G209" s="9" t="inlineStr">
         <is>
-          <t>Г_Ж_1_курс_2026-2027_Фэб_фдтио_Фиит.xlsx</t>
+          <t>1_kurs.xlsx</t>
         </is>
       </c>
       <c r="H209" s="9" t="inlineStr">
@@ -10084,7 +10084,7 @@
       </c>
       <c r="G210" s="9" t="inlineStr">
         <is>
-          <t>Г_Ж_1_курс_2026-2027_Фэб_фдтио_Фиит.xlsx</t>
+          <t>1_kurs.xlsx</t>
         </is>
       </c>
       <c r="H210" s="9" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="G211" s="9" t="inlineStr">
         <is>
-          <t>Г_Ж_1_курс_2026-2027_Фэб_фдтио_Фиит.xlsx</t>
+          <t>1_kurs.xlsx</t>
         </is>
       </c>
       <c r="H211" s="9" t="inlineStr">
@@ -10168,7 +10168,7 @@
       </c>
       <c r="G212" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H212" s="9" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="G213" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H213" s="9" t="inlineStr">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="G214" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H214" s="9" t="inlineStr">
@@ -10294,7 +10294,7 @@
       </c>
       <c r="G215" s="9" t="inlineStr">
         <is>
-          <t>Расписание_магистрантов_2_курс.xlsx</t>
+          <t>magistratura_2kurs.xlsx</t>
         </is>
       </c>
       <c r="H215" s="9" t="inlineStr">
@@ -10336,7 +10336,7 @@
       </c>
       <c r="G216" s="9" t="inlineStr">
         <is>
-          <t>МАГИСТРАТУРА_1_КУРС_ПРОФИЛЬНОЕ_НАПР__2026-2027_г_.xlsx</t>
+          <t>magistratura_profil.xlsx</t>
         </is>
       </c>
       <c r="H216" s="9" t="inlineStr">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="G217" s="9" t="inlineStr">
         <is>
-          <t>МАГИСТРАТУРА_1_КУРС_ПРОФИЛЬНОЕ_НАПР__2026-2027_г_.xlsx</t>
+          <t>magistratura_profil.xlsx</t>
         </is>
       </c>
       <c r="H217" s="9" t="inlineStr">
@@ -10420,7 +10420,7 @@
       </c>
       <c r="G218" s="9" t="inlineStr">
         <is>
-          <t>МАГИСТРАТУРА_1_КУРС_ПРОФИЛЬНОЕ_НАПР__2026-2027_г_.xlsx</t>
+          <t>magistratura_profil.xlsx</t>
         </is>
       </c>
       <c r="H218" s="9" t="inlineStr">
@@ -10462,7 +10462,7 @@
       </c>
       <c r="G219" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H219" s="9" t="inlineStr">
@@ -10504,7 +10504,7 @@
       </c>
       <c r="G220" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H220" s="9" t="inlineStr">
@@ -10546,7 +10546,7 @@
       </c>
       <c r="G221" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H221" s="9" t="inlineStr">
@@ -10588,7 +10588,7 @@
       </c>
       <c r="G222" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H222" s="9" t="inlineStr">
@@ -10630,7 +10630,7 @@
       </c>
       <c r="G223" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H223" s="9" t="inlineStr">
@@ -10672,7 +10672,7 @@
       </c>
       <c r="G224" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H224" s="9" t="inlineStr">
@@ -10714,7 +10714,7 @@
       </c>
       <c r="G225" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H225" s="9" t="inlineStr">
@@ -10756,7 +10756,7 @@
       </c>
       <c r="G226" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H226" s="9" t="inlineStr">
@@ -10798,7 +10798,7 @@
       </c>
       <c r="G227" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H227" s="9" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="G228" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H228" s="9" t="inlineStr">
@@ -10882,7 +10882,7 @@
       </c>
       <c r="G229" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H229" s="9" t="inlineStr">
@@ -10924,7 +10924,7 @@
       </c>
       <c r="G230" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H230" s="9" t="inlineStr">
@@ -10966,7 +10966,7 @@
       </c>
       <c r="G231" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H231" s="9" t="inlineStr">
@@ -11008,7 +11008,7 @@
       </c>
       <c r="G232" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H232" s="9" t="inlineStr">
@@ -11050,7 +11050,7 @@
       </c>
       <c r="G233" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H233" s="9" t="inlineStr">
@@ -11092,7 +11092,7 @@
       </c>
       <c r="G234" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H234" s="9" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="G235" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H235" s="9" t="inlineStr">
@@ -11176,7 +11176,7 @@
       </c>
       <c r="G236" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H236" s="9" t="inlineStr">
@@ -11218,7 +11218,7 @@
       </c>
       <c r="G237" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H237" s="9" t="inlineStr">
@@ -11256,7 +11256,7 @@
       </c>
       <c r="G238" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H238" s="9" t="inlineStr">
@@ -11298,7 +11298,7 @@
       </c>
       <c r="G239" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H239" s="9" t="inlineStr">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="G240" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H240" s="9" t="inlineStr">
@@ -11382,7 +11382,7 @@
       </c>
       <c r="G241" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H241" s="9" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="G242" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H242" s="9" t="inlineStr">
@@ -11466,7 +11466,7 @@
       </c>
       <c r="G243" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H243" s="9" t="inlineStr">
@@ -11508,7 +11508,7 @@
       </c>
       <c r="G244" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H244" s="9" t="inlineStr">
@@ -11550,7 +11550,7 @@
       </c>
       <c r="G245" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H245" s="9" t="inlineStr">
@@ -11592,7 +11592,7 @@
       </c>
       <c r="G246" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H246" s="9" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="G247" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H247" s="9" t="inlineStr">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="G248" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H248" s="9" t="inlineStr">
@@ -11718,7 +11718,7 @@
       </c>
       <c r="G249" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H249" s="9" t="inlineStr">
@@ -11760,7 +11760,7 @@
       </c>
       <c r="G250" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H250" s="9" t="inlineStr">
@@ -11802,7 +11802,7 @@
       </c>
       <c r="G251" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H251" s="9" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="G252" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H252" s="9" t="inlineStr">
@@ -11886,7 +11886,7 @@
       </c>
       <c r="G253" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H253" s="9" t="inlineStr">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="G254" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H254" s="9" t="inlineStr">
@@ -11970,7 +11970,7 @@
       </c>
       <c r="G255" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H255" s="9" t="inlineStr">
@@ -12012,7 +12012,7 @@
       </c>
       <c r="G256" s="9" t="inlineStr">
         <is>
-          <t>Расписание_магистрантов_2_курс.xlsx</t>
+          <t>magistratura_2kurs.xlsx</t>
         </is>
       </c>
       <c r="H256" s="9" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="G257" s="9" t="inlineStr">
         <is>
-          <t>Расписание_магистрантов_2_курс.xlsx</t>
+          <t>magistratura_2kurs.xlsx</t>
         </is>
       </c>
       <c r="H257" s="9" t="inlineStr">
@@ -12096,7 +12096,7 @@
       </c>
       <c r="G258" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H258" s="9" t="inlineStr">
@@ -12138,7 +12138,7 @@
       </c>
       <c r="G259" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H259" s="9" t="inlineStr">
@@ -12180,7 +12180,7 @@
       </c>
       <c r="G260" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H260" s="9" t="inlineStr">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="G261" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H261" s="9" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="G262" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H262" s="9" t="inlineStr">
@@ -12306,7 +12306,7 @@
       </c>
       <c r="G263" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H263" s="9" t="inlineStr">
@@ -12348,7 +12348,7 @@
       </c>
       <c r="G264" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H264" s="9" t="inlineStr">
@@ -12390,7 +12390,7 @@
       </c>
       <c r="G265" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H265" s="9" t="inlineStr">
@@ -12432,7 +12432,7 @@
       </c>
       <c r="G266" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H266" s="9" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="G267" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H267" s="9" t="inlineStr">
@@ -12516,7 +12516,7 @@
       </c>
       <c r="G268" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H268" s="9" t="inlineStr">
@@ -12558,7 +12558,7 @@
       </c>
       <c r="G269" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H269" s="9" t="inlineStr">
@@ -12600,7 +12600,7 @@
       </c>
       <c r="G270" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H270" s="9" t="inlineStr">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="G271" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H271" s="9" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="G272" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H272" s="9" t="inlineStr">
@@ -12726,7 +12726,7 @@
       </c>
       <c r="G273" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H273" s="9" t="inlineStr">
@@ -12768,7 +12768,7 @@
       </c>
       <c r="G274" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H274" s="9" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="G275" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H275" s="9" t="inlineStr">
@@ -12852,7 +12852,7 @@
       </c>
       <c r="G276" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H276" s="9" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="G277" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H277" s="9" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="G278" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H278" s="9" t="inlineStr">
@@ -12978,7 +12978,7 @@
       </c>
       <c r="G279" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H279" s="9" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="G280" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H280" s="9" t="inlineStr">
@@ -13062,7 +13062,7 @@
       </c>
       <c r="G281" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H281" s="9" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="G282" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H282" s="9" t="inlineStr">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="G283" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H283" s="9" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="G284" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H284" s="9" t="inlineStr">
@@ -13230,7 +13230,7 @@
       </c>
       <c r="G285" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H285" s="9" t="inlineStr">
@@ -13272,7 +13272,7 @@
       </c>
       <c r="G286" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H286" s="9" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="G287" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H287" s="9" t="inlineStr">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="G288" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H288" s="9" t="inlineStr">
@@ -13398,7 +13398,7 @@
       </c>
       <c r="G289" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H289" s="9" t="inlineStr">
@@ -13440,7 +13440,7 @@
       </c>
       <c r="G290" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H290" s="9" t="inlineStr">
@@ -13482,7 +13482,7 @@
       </c>
       <c r="G291" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H291" s="9" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="G292" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H292" s="9" t="inlineStr">
@@ -13566,7 +13566,7 @@
       </c>
       <c r="G293" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H293" s="9" t="inlineStr">
@@ -13608,7 +13608,7 @@
       </c>
       <c r="G294" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H294" s="9" t="inlineStr">
@@ -13650,7 +13650,7 @@
       </c>
       <c r="G295" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H295" s="9" t="inlineStr">
@@ -13692,7 +13692,7 @@
       </c>
       <c r="G296" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H296" s="9" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="G297" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H297" s="9" t="inlineStr">
@@ -13776,7 +13776,7 @@
       </c>
       <c r="G298" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H298" s="9" t="inlineStr">
@@ -13818,7 +13818,7 @@
       </c>
       <c r="G299" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H299" s="9" t="inlineStr">
@@ -13860,7 +13860,7 @@
       </c>
       <c r="G300" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H300" s="9" t="inlineStr">
@@ -13902,7 +13902,7 @@
       </c>
       <c r="G301" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H301" s="9" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="G302" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H302" s="9" t="inlineStr">
@@ -13986,7 +13986,7 @@
       </c>
       <c r="G303" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H303" s="9" t="inlineStr">
@@ -14028,7 +14028,7 @@
       </c>
       <c r="G304" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H304" s="9" t="inlineStr">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="G305" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H305" s="9" t="inlineStr">
@@ -14112,7 +14112,7 @@
       </c>
       <c r="G306" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H306" s="9" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="G307" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H307" s="9" t="inlineStr">
@@ -14196,7 +14196,7 @@
       </c>
       <c r="G308" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H308" s="9" t="inlineStr">
@@ -14238,7 +14238,7 @@
       </c>
       <c r="G309" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H309" s="9" t="inlineStr">
@@ -14280,7 +14280,7 @@
       </c>
       <c r="G310" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H310" s="9" t="inlineStr">
@@ -14322,7 +14322,7 @@
       </c>
       <c r="G311" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H311" s="9" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="G312" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H312" s="9" t="inlineStr">
@@ -14406,7 +14406,7 @@
       </c>
       <c r="G313" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H313" s="9" t="inlineStr">
@@ -14448,7 +14448,7 @@
       </c>
       <c r="G314" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H314" s="9" t="inlineStr">
@@ -14490,7 +14490,7 @@
       </c>
       <c r="G315" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H315" s="9" t="inlineStr">
@@ -14532,7 +14532,7 @@
       </c>
       <c r="G316" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H316" s="9" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="G317" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H317" s="9" t="inlineStr">
@@ -14616,7 +14616,7 @@
       </c>
       <c r="G318" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H318" s="9" t="inlineStr">
@@ -14658,7 +14658,7 @@
       </c>
       <c r="G319" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H319" s="9" t="inlineStr">
@@ -14700,7 +14700,7 @@
       </c>
       <c r="G320" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H320" s="9" t="inlineStr">
@@ -14742,7 +14742,7 @@
       </c>
       <c r="G321" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H321" s="9" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="G322" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H322" s="9" t="inlineStr">
@@ -14826,7 +14826,7 @@
       </c>
       <c r="G323" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H323" s="9" t="inlineStr">
@@ -14868,7 +14868,7 @@
       </c>
       <c r="G324" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H324" s="9" t="inlineStr">
@@ -14910,7 +14910,7 @@
       </c>
       <c r="G325" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H325" s="9" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="G326" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H326" s="9" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="G327" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H327" s="9" t="inlineStr">
@@ -15036,7 +15036,7 @@
       </c>
       <c r="G328" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H328" s="9" t="inlineStr">
@@ -15078,7 +15078,7 @@
       </c>
       <c r="G329" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H329" s="9" t="inlineStr">
@@ -15120,7 +15120,7 @@
       </c>
       <c r="G330" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H330" s="9" t="inlineStr">
@@ -15162,7 +15162,7 @@
       </c>
       <c r="G331" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H331" s="9" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="G332" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H332" s="9" t="inlineStr">
@@ -15246,7 +15246,7 @@
       </c>
       <c r="G333" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H333" s="9" t="inlineStr">
@@ -15288,7 +15288,7 @@
       </c>
       <c r="G334" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H334" s="9" t="inlineStr">
@@ -15330,7 +15330,7 @@
       </c>
       <c r="G335" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H335" s="9" t="inlineStr">
@@ -15372,7 +15372,7 @@
       </c>
       <c r="G336" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H336" s="9" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="G337" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H337" s="9" t="inlineStr">
@@ -15456,7 +15456,7 @@
       </c>
       <c r="G338" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H338" s="9" t="inlineStr">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="G339" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H339" s="9" t="inlineStr">
@@ -15540,7 +15540,7 @@
       </c>
       <c r="G340" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H340" s="9" t="inlineStr">
@@ -15582,7 +15582,7 @@
       </c>
       <c r="G341" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H341" s="9" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="G342" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H342" s="9" t="inlineStr">
@@ -15666,7 +15666,7 @@
       </c>
       <c r="G343" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H343" s="9" t="inlineStr">
@@ -15708,7 +15708,7 @@
       </c>
       <c r="G344" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H344" s="9" t="inlineStr">
@@ -15750,7 +15750,7 @@
       </c>
       <c r="G345" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H345" s="9" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="G346" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H346" s="9" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="G347" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H347" s="9" t="inlineStr">
@@ -15876,7 +15876,7 @@
       </c>
       <c r="G348" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H348" s="9" t="inlineStr">
@@ -15918,7 +15918,7 @@
       </c>
       <c r="G349" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H349" s="9" t="inlineStr">
@@ -15960,7 +15960,7 @@
       </c>
       <c r="G350" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H350" s="9" t="inlineStr">
@@ -16002,7 +16002,7 @@
       </c>
       <c r="G351" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H351" s="9" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="G352" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H352" s="9" t="inlineStr">
@@ -16086,7 +16086,7 @@
       </c>
       <c r="G353" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H353" s="9" t="inlineStr">
@@ -16128,7 +16128,7 @@
       </c>
       <c r="G354" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H354" s="9" t="inlineStr">
@@ -16170,7 +16170,7 @@
       </c>
       <c r="G355" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H355" s="9" t="inlineStr">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="G356" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H356" s="9" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="G357" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H357" s="9" t="inlineStr">
@@ -16296,7 +16296,7 @@
       </c>
       <c r="G358" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H358" s="9" t="inlineStr">
@@ -16338,7 +16338,7 @@
       </c>
       <c r="G359" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H359" s="9" t="inlineStr">
@@ -16380,7 +16380,7 @@
       </c>
       <c r="G360" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H360" s="9" t="inlineStr">
@@ -16422,7 +16422,7 @@
       </c>
       <c r="G361" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H361" s="9" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="G362" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H362" s="9" t="inlineStr">
@@ -16506,7 +16506,7 @@
       </c>
       <c r="G363" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H363" s="9" t="inlineStr">
@@ -16548,7 +16548,7 @@
       </c>
       <c r="G364" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H364" s="9" t="inlineStr">
@@ -16590,7 +16590,7 @@
       </c>
       <c r="G365" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H365" s="9" t="inlineStr">
@@ -16632,7 +16632,7 @@
       </c>
       <c r="G366" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H366" s="9" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="G367" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H367" s="9" t="inlineStr">
@@ -16716,7 +16716,7 @@
       </c>
       <c r="G368" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H368" s="9" t="inlineStr">
@@ -16758,7 +16758,7 @@
       </c>
       <c r="G369" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H369" s="9" t="inlineStr">
@@ -16800,7 +16800,7 @@
       </c>
       <c r="G370" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H370" s="9" t="inlineStr">
@@ -16842,7 +16842,7 @@
       </c>
       <c r="G371" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H371" s="9" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="G372" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H372" s="9" t="inlineStr">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="G373" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H373" s="9" t="inlineStr">
@@ -16968,7 +16968,7 @@
       </c>
       <c r="G374" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H374" s="9" t="inlineStr">
@@ -17010,7 +17010,7 @@
       </c>
       <c r="G375" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H375" s="9" t="inlineStr">
@@ -17052,7 +17052,7 @@
       </c>
       <c r="G376" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H376" s="9" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="G377" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H377" s="9" t="inlineStr">
@@ -17136,7 +17136,7 @@
       </c>
       <c r="G378" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H378" s="9" t="inlineStr">
@@ -17178,7 +17178,7 @@
       </c>
       <c r="G379" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H379" s="9" t="inlineStr">
@@ -17220,7 +17220,7 @@
       </c>
       <c r="G380" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H380" s="9" t="inlineStr">
@@ -17262,7 +17262,7 @@
       </c>
       <c r="G381" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H381" s="9" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="G382" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H382" s="9" t="inlineStr">
@@ -17346,7 +17346,7 @@
       </c>
       <c r="G383" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H383" s="9" t="inlineStr">
@@ -17388,7 +17388,7 @@
       </c>
       <c r="G384" s="9" t="inlineStr">
         <is>
-          <t>Г_Ж_1_курс_2026-2027_Фэб_фдтио_Фиит.xlsx</t>
+          <t>1_kurs.xlsx</t>
         </is>
       </c>
       <c r="H384" s="9" t="inlineStr">
@@ -17430,7 +17430,7 @@
       </c>
       <c r="G385" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H385" s="9" t="inlineStr">
@@ -17472,7 +17472,7 @@
       </c>
       <c r="G386" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H386" s="9" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="G387" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H387" s="9" t="inlineStr">
@@ -17556,7 +17556,7 @@
       </c>
       <c r="G388" s="9" t="inlineStr">
         <is>
-          <t>Г_Ж_1_курс_2026-2027_Фэб_фдтио_Фиит.xlsx</t>
+          <t>1_kurs.xlsx</t>
         </is>
       </c>
       <c r="H388" s="9" t="inlineStr">
@@ -17598,7 +17598,7 @@
       </c>
       <c r="G389" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H389" s="9" t="inlineStr">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="G390" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H390" s="9" t="inlineStr">
@@ -17682,7 +17682,7 @@
       </c>
       <c r="G391" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H391" s="9" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="G392" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H392" s="9" t="inlineStr">
@@ -17766,7 +17766,7 @@
       </c>
       <c r="G393" s="9" t="inlineStr">
         <is>
-          <t>Г_Ж_1_курс_2026-2027_Фэб_фдтио_Фиит.xlsx</t>
+          <t>1_kurs.xlsx</t>
         </is>
       </c>
       <c r="H393" s="9" t="inlineStr">
@@ -17808,7 +17808,7 @@
       </c>
       <c r="G394" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H394" s="9" t="inlineStr">
@@ -17850,7 +17850,7 @@
       </c>
       <c r="G395" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H395" s="9" t="inlineStr">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="G396" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H396" s="9" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="G397" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H397" s="9" t="inlineStr">
@@ -17976,7 +17976,7 @@
       </c>
       <c r="G398" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H398" s="9" t="inlineStr">
@@ -18018,7 +18018,7 @@
       </c>
       <c r="G399" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H399" s="9" t="inlineStr">
@@ -18060,7 +18060,7 @@
       </c>
       <c r="G400" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H400" s="9" t="inlineStr">
@@ -18102,7 +18102,7 @@
       </c>
       <c r="G401" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H401" s="9" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="G402" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H402" s="9" t="inlineStr">
@@ -18186,7 +18186,7 @@
       </c>
       <c r="G403" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H403" s="9" t="inlineStr">
@@ -18228,7 +18228,7 @@
       </c>
       <c r="G404" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H404" s="9" t="inlineStr">
@@ -18270,7 +18270,7 @@
       </c>
       <c r="G405" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H405" s="9" t="inlineStr">
@@ -18312,7 +18312,7 @@
       </c>
       <c r="G406" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H406" s="9" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="G407" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H407" s="9" t="inlineStr">
@@ -18396,7 +18396,7 @@
       </c>
       <c r="G408" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H408" s="9" t="inlineStr">
@@ -18438,7 +18438,7 @@
       </c>
       <c r="G409" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H409" s="9" t="inlineStr">
@@ -18480,7 +18480,7 @@
       </c>
       <c r="G410" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H410" s="9" t="inlineStr">
@@ -18522,7 +18522,7 @@
       </c>
       <c r="G411" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H411" s="9" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="G412" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H412" s="9" t="inlineStr">
@@ -18606,7 +18606,7 @@
       </c>
       <c r="G413" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H413" s="9" t="inlineStr">
@@ -18648,7 +18648,7 @@
       </c>
       <c r="G414" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H414" s="9" t="inlineStr">
@@ -18690,7 +18690,7 @@
       </c>
       <c r="G415" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H415" s="9" t="inlineStr">
@@ -18732,7 +18732,7 @@
       </c>
       <c r="G416" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H416" s="9" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="G417" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H417" s="9" t="inlineStr">
@@ -18816,7 +18816,7 @@
       </c>
       <c r="G418" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H418" s="9" t="inlineStr">
@@ -18858,7 +18858,7 @@
       </c>
       <c r="G419" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H419" s="9" t="inlineStr">
@@ -18900,7 +18900,7 @@
       </c>
       <c r="G420" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H420" s="9" t="inlineStr">
@@ -18942,7 +18942,7 @@
       </c>
       <c r="G421" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H421" s="9" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="G422" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H422" s="9" t="inlineStr">
@@ -19026,7 +19026,7 @@
       </c>
       <c r="G423" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H423" s="9" t="inlineStr">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="G424" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H424" s="9" t="inlineStr">
@@ -19110,7 +19110,7 @@
       </c>
       <c r="G425" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H425" s="9" t="inlineStr">
@@ -19152,7 +19152,7 @@
       </c>
       <c r="G426" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H426" s="9" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="G427" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H427" s="9" t="inlineStr">
@@ -19236,7 +19236,7 @@
       </c>
       <c r="G428" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H428" s="9" t="inlineStr">
@@ -19278,7 +19278,7 @@
       </c>
       <c r="G429" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H429" s="9" t="inlineStr">
@@ -19320,7 +19320,7 @@
       </c>
       <c r="G430" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H430" s="9" t="inlineStr">
@@ -19358,7 +19358,7 @@
       </c>
       <c r="G431" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H431" s="9" t="inlineStr">
@@ -19396,7 +19396,7 @@
       </c>
       <c r="G432" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
       <c r="H432" s="9" t="inlineStr">
@@ -19438,7 +19438,7 @@
       </c>
       <c r="G433" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H433" s="9" t="inlineStr">
@@ -19480,7 +19480,7 @@
       </c>
       <c r="G434" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H434" s="9" t="inlineStr">
@@ -19522,7 +19522,7 @@
       </c>
       <c r="G435" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H435" s="9" t="inlineStr">
@@ -19564,7 +19564,7 @@
       </c>
       <c r="G436" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H436" s="9" t="inlineStr">
@@ -19606,7 +19606,7 @@
       </c>
       <c r="G437" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H437" s="9" t="inlineStr">
@@ -19648,7 +19648,7 @@
       </c>
       <c r="G438" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H438" s="9" t="inlineStr">
@@ -19690,7 +19690,7 @@
       </c>
       <c r="G439" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H439" s="9" t="inlineStr">
@@ -19732,7 +19732,7 @@
       </c>
       <c r="G440" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H440" s="9" t="inlineStr">
@@ -19774,7 +19774,7 @@
       </c>
       <c r="G441" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H441" s="9" t="inlineStr">
@@ -19816,7 +19816,7 @@
       </c>
       <c r="G442" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
       <c r="H442" s="9" t="inlineStr">
@@ -19858,7 +19858,7 @@
       </c>
       <c r="G443" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H443" s="9" t="inlineStr">
@@ -19900,7 +19900,7 @@
       </c>
       <c r="G444" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
       <c r="H444" s="9" t="inlineStr">
@@ -20006,7 +20006,7 @@
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>МАГИСТРАТУРА_1_КУРС_ПРОФИЛЬНОЕ_НАПР__2026-2027_г_.xlsx</t>
+          <t>magistratura_profil.xlsx</t>
         </is>
       </c>
     </row>
@@ -20038,7 +20038,7 @@
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>МАГИСТРАТУРА_1_КУРС_ПРОФИЛЬНОЕ_НАПР__2026-2027_г_.xlsx</t>
+          <t>magistratura_profil.xlsx</t>
         </is>
       </c>
     </row>
@@ -20109,7 +20109,7 @@
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -20141,7 +20141,7 @@
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -20173,7 +20173,7 @@
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>Расписание_магистрантов_1_КУРС_НАУЧНО-ПЕД__НАПРАВЛЕНИЕ__2026-2027_уч_г_.xlsx</t>
+          <t>magistratura_nauchped.xlsx</t>
         </is>
       </c>
     </row>
@@ -20205,7 +20205,7 @@
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>Расписание_магистрантов_1_КУРС_НАУЧНО-ПЕД__НАПРАВЛЕНИЕ__2026-2027_уч_г_.xlsx</t>
+          <t>magistratura_nauchped.xlsx</t>
         </is>
       </c>
     </row>
@@ -20237,7 +20237,7 @@
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -20269,7 +20269,7 @@
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -20301,7 +20301,7 @@
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -20333,7 +20333,7 @@
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -20365,7 +20365,7 @@
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -20397,7 +20397,7 @@
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -20429,7 +20429,7 @@
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>МАГИСТРАТУРА_1_КУРС_ПРОФИЛЬНОЕ_НАПР__2026-2027_г_.xlsx</t>
+          <t>magistratura_profil.xlsx</t>
         </is>
       </c>
     </row>
@@ -20461,7 +20461,7 @@
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>МАГИСТРАТУРА_1_КУРС_ПРОФИЛЬНОЕ_НАПР__2026-2027_г_.xlsx</t>
+          <t>magistratura_profil.xlsx</t>
         </is>
       </c>
     </row>
@@ -20493,7 +20493,7 @@
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>Расписание_магистрантов_1_КУРС_НАУЧНО-ПЕД__НАПРАВЛЕНИЕ__2026-2027_уч_г_.xlsx</t>
+          <t>magistratura_nauchped.xlsx</t>
         </is>
       </c>
     </row>
@@ -20525,7 +20525,7 @@
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>Расписание_магистрантов_1_КУРС_НАУЧНО-ПЕД__НАПРАВЛЕНИЕ__2026-2027_уч_г_.xlsx</t>
+          <t>magistratura_nauchped.xlsx</t>
         </is>
       </c>
     </row>
@@ -20557,7 +20557,7 @@
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -20589,7 +20589,7 @@
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -20660,7 +20660,7 @@
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>Расписание_магистрантов_2_курс.xlsx</t>
+          <t>magistratura_2kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -20692,7 +20692,7 @@
       </c>
       <c r="F30" s="9" t="inlineStr">
         <is>
-          <t>Расписание_магистрантов_2_курс.xlsx</t>
+          <t>magistratura_2kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -20763,7 +20763,7 @@
       </c>
       <c r="F34" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -20834,7 +20834,7 @@
       </c>
       <c r="F38" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -20866,7 +20866,7 @@
       </c>
       <c r="F39" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -20898,7 +20898,7 @@
       </c>
       <c r="F40" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -20930,7 +20930,7 @@
       </c>
       <c r="F41" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -20962,7 +20962,7 @@
       </c>
       <c r="F42" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -20994,7 +20994,7 @@
       </c>
       <c r="F43" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -21026,7 +21026,7 @@
       </c>
       <c r="F44" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -21058,7 +21058,7 @@
       </c>
       <c r="F45" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -21090,7 +21090,7 @@
       </c>
       <c r="F46" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -21122,7 +21122,7 @@
       </c>
       <c r="F47" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -21154,7 +21154,7 @@
       </c>
       <c r="F48" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -21182,7 +21182,7 @@
       </c>
       <c r="F49" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="F50" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -21281,7 +21281,7 @@
       </c>
       <c r="F54" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -21313,7 +21313,7 @@
       </c>
       <c r="F55" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -21345,7 +21345,7 @@
       </c>
       <c r="F56" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -21377,7 +21377,7 @@
       </c>
       <c r="F57" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -21409,7 +21409,7 @@
       </c>
       <c r="F58" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -21441,7 +21441,7 @@
       </c>
       <c r="F59" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -21473,7 +21473,7 @@
       </c>
       <c r="F60" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -21505,7 +21505,7 @@
       </c>
       <c r="F61" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -21537,7 +21537,7 @@
       </c>
       <c r="F62" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -21569,7 +21569,7 @@
       </c>
       <c r="F63" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -21601,7 +21601,7 @@
       </c>
       <c r="F64" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -21633,7 +21633,7 @@
       </c>
       <c r="F65" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -21665,7 +21665,7 @@
       </c>
       <c r="F66" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -21697,7 +21697,7 @@
       </c>
       <c r="F67" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -21729,7 +21729,7 @@
       </c>
       <c r="F68" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -21761,7 +21761,7 @@
       </c>
       <c r="F69" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -21793,7 +21793,7 @@
       </c>
       <c r="F70" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -21864,7 +21864,7 @@
       </c>
       <c r="F74" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -21896,7 +21896,7 @@
       </c>
       <c r="F75" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -21928,7 +21928,7 @@
       </c>
       <c r="F76" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -21960,7 +21960,7 @@
       </c>
       <c r="F77" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -21992,7 +21992,7 @@
       </c>
       <c r="F78" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -22024,7 +22024,7 @@
       </c>
       <c r="F79" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -22056,7 +22056,7 @@
       </c>
       <c r="F80" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -22088,7 +22088,7 @@
       </c>
       <c r="F81" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -22120,7 +22120,7 @@
       </c>
       <c r="F82" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -22152,7 +22152,7 @@
       </c>
       <c r="F83" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -22184,7 +22184,7 @@
       </c>
       <c r="F84" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -22216,7 +22216,7 @@
       </c>
       <c r="F85" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -22248,7 +22248,7 @@
       </c>
       <c r="F86" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -22280,7 +22280,7 @@
       </c>
       <c r="F87" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -22312,7 +22312,7 @@
       </c>
       <c r="F88" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -22344,7 +22344,7 @@
       </c>
       <c r="F89" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -22415,7 +22415,7 @@
       </c>
       <c r="F93" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -22447,7 +22447,7 @@
       </c>
       <c r="F94" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -22479,7 +22479,7 @@
       </c>
       <c r="F95" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -22511,7 +22511,7 @@
       </c>
       <c r="F96" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -22543,7 +22543,7 @@
       </c>
       <c r="F97" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -22575,7 +22575,7 @@
       </c>
       <c r="F98" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -22607,7 +22607,7 @@
       </c>
       <c r="F99" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -22639,7 +22639,7 @@
       </c>
       <c r="F100" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -22671,7 +22671,7 @@
       </c>
       <c r="F101" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -22703,7 +22703,7 @@
       </c>
       <c r="F102" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -22735,7 +22735,7 @@
       </c>
       <c r="F103" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -22767,7 +22767,7 @@
       </c>
       <c r="F104" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -22799,7 +22799,7 @@
       </c>
       <c r="F105" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -22831,7 +22831,7 @@
       </c>
       <c r="F106" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -22863,7 +22863,7 @@
       </c>
       <c r="F107" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -22895,7 +22895,7 @@
       </c>
       <c r="F108" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -22927,7 +22927,7 @@
       </c>
       <c r="F109" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -22959,7 +22959,7 @@
       </c>
       <c r="F110" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -22991,7 +22991,7 @@
       </c>
       <c r="F111" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -23023,7 +23023,7 @@
       </c>
       <c r="F112" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -23055,7 +23055,7 @@
       </c>
       <c r="F113" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -23087,7 +23087,7 @@
       </c>
       <c r="F114" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -23119,7 +23119,7 @@
       </c>
       <c r="F115" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -23190,7 +23190,7 @@
       </c>
       <c r="F119" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -23222,7 +23222,7 @@
       </c>
       <c r="F120" s="9" t="inlineStr">
         <is>
-          <t>Г_Ж_1_курс_2026-2027_Фэб_фдтио_Фиит.xlsx</t>
+          <t>1_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -23254,7 +23254,7 @@
       </c>
       <c r="F121" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -23286,7 +23286,7 @@
       </c>
       <c r="F122" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -23318,7 +23318,7 @@
       </c>
       <c r="F123" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -23350,7 +23350,7 @@
       </c>
       <c r="F124" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -23382,7 +23382,7 @@
       </c>
       <c r="F125" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="F126" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -23446,7 +23446,7 @@
       </c>
       <c r="F127" s="9" t="inlineStr">
         <is>
-          <t>Г_Ж_1_курс_2026-2027_Фэб_фдтио_Фиит.xlsx</t>
+          <t>1_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -23478,7 +23478,7 @@
       </c>
       <c r="F128" s="9" t="inlineStr">
         <is>
-          <t>Г_Ж_1_курс_2026-2027_Фэб_фдтио_Фиит.xlsx</t>
+          <t>1_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -23510,7 +23510,7 @@
       </c>
       <c r="F129" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -23542,7 +23542,7 @@
       </c>
       <c r="F130" s="9" t="inlineStr">
         <is>
-          <t>Расписание_магистрантов_2_курс.xlsx</t>
+          <t>magistratura_2kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -23574,7 +23574,7 @@
       </c>
       <c r="F131" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -23606,7 +23606,7 @@
       </c>
       <c r="F132" s="9" t="inlineStr">
         <is>
-          <t>Расписание_магистрантов_2_курс.xlsx</t>
+          <t>magistratura_2kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -23638,7 +23638,7 @@
       </c>
       <c r="F133" s="9" t="inlineStr">
         <is>
-          <t>Г_Ж_1_курс_2026-2027_Фэб_фдтио_Фиит.xlsx</t>
+          <t>1_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -23670,7 +23670,7 @@
       </c>
       <c r="F134" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -23702,7 +23702,7 @@
       </c>
       <c r="F135" s="9" t="inlineStr">
         <is>
-          <t>Г_Ж_1_курс_2026-2027_Фэб_фдтио_Фиит.xlsx</t>
+          <t>1_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -23734,7 +23734,7 @@
       </c>
       <c r="F136" s="9" t="inlineStr">
         <is>
-          <t>Расписание_магистрантов_2_курс.xlsx</t>
+          <t>magistratura_2kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -23766,7 +23766,7 @@
       </c>
       <c r="F137" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -23798,7 +23798,7 @@
       </c>
       <c r="F138" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -23830,7 +23830,7 @@
       </c>
       <c r="F139" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -23862,7 +23862,7 @@
       </c>
       <c r="F140" s="9" t="inlineStr">
         <is>
-          <t>Г_Ж_1_курс_2026-2027_Фэб_фдтио_Фиит.xlsx</t>
+          <t>1_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -23894,7 +23894,7 @@
       </c>
       <c r="F141" s="9" t="inlineStr">
         <is>
-          <t>Г_Ж_1_курс_2026-2027_Фэб_фдтио_Фиит.xlsx</t>
+          <t>1_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -23926,7 +23926,7 @@
       </c>
       <c r="F142" s="9" t="inlineStr">
         <is>
-          <t>Г_Ж_1_курс_2026-2027_Фэб_фдтио_Фиит.xlsx</t>
+          <t>1_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -23958,7 +23958,7 @@
       </c>
       <c r="F143" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -23990,7 +23990,7 @@
       </c>
       <c r="F144" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -24061,7 +24061,7 @@
       </c>
       <c r="F148" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -24093,7 +24093,7 @@
       </c>
       <c r="F149" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -24125,7 +24125,7 @@
       </c>
       <c r="F150" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -24157,7 +24157,7 @@
       </c>
       <c r="F151" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -24189,7 +24189,7 @@
       </c>
       <c r="F152" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -24221,7 +24221,7 @@
       </c>
       <c r="F153" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -24253,7 +24253,7 @@
       </c>
       <c r="F154" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -24285,7 +24285,7 @@
       </c>
       <c r="F155" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -24317,7 +24317,7 @@
       </c>
       <c r="F156" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -24349,7 +24349,7 @@
       </c>
       <c r="F157" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -24377,7 +24377,7 @@
       </c>
       <c r="F158" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -24448,7 +24448,7 @@
       </c>
       <c r="F162" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -24480,7 +24480,7 @@
       </c>
       <c r="F163" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -24512,7 +24512,7 @@
       </c>
       <c r="F164" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -24544,7 +24544,7 @@
       </c>
       <c r="F165" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -24576,7 +24576,7 @@
       </c>
       <c r="F166" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -24608,7 +24608,7 @@
       </c>
       <c r="F167" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -24640,7 +24640,7 @@
       </c>
       <c r="F168" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -24672,7 +24672,7 @@
       </c>
       <c r="F169" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -24704,7 +24704,7 @@
       </c>
       <c r="F170" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -24736,7 +24736,7 @@
       </c>
       <c r="F171" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -24768,7 +24768,7 @@
       </c>
       <c r="F172" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -24800,7 +24800,7 @@
       </c>
       <c r="F173" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -24832,7 +24832,7 @@
       </c>
       <c r="F174" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -24864,7 +24864,7 @@
       </c>
       <c r="F175" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -24896,7 +24896,7 @@
       </c>
       <c r="F176" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -24967,7 +24967,7 @@
       </c>
       <c r="F180" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -24999,7 +24999,7 @@
       </c>
       <c r="F181" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -25031,7 +25031,7 @@
       </c>
       <c r="F182" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -25063,7 +25063,7 @@
       </c>
       <c r="F183" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -25095,7 +25095,7 @@
       </c>
       <c r="F184" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -25127,7 +25127,7 @@
       </c>
       <c r="F185" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -25159,7 +25159,7 @@
       </c>
       <c r="F186" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -25191,7 +25191,7 @@
       </c>
       <c r="F187" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -25223,7 +25223,7 @@
       </c>
       <c r="F188" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -25255,7 +25255,7 @@
       </c>
       <c r="F189" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -25326,7 +25326,7 @@
       </c>
       <c r="F193" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -25358,7 +25358,7 @@
       </c>
       <c r="F194" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -25390,7 +25390,7 @@
       </c>
       <c r="F195" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -25422,7 +25422,7 @@
       </c>
       <c r="F196" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -25454,7 +25454,7 @@
       </c>
       <c r="F197" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -25486,7 +25486,7 @@
       </c>
       <c r="F198" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -25518,7 +25518,7 @@
       </c>
       <c r="F199" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -25550,7 +25550,7 @@
       </c>
       <c r="F200" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -25582,7 +25582,7 @@
       </c>
       <c r="F201" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -25614,7 +25614,7 @@
       </c>
       <c r="F202" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -25646,7 +25646,7 @@
       </c>
       <c r="F203" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -25678,7 +25678,7 @@
       </c>
       <c r="F204" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -25710,7 +25710,7 @@
       </c>
       <c r="F205" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -25781,7 +25781,7 @@
       </c>
       <c r="F209" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -25813,7 +25813,7 @@
       </c>
       <c r="F210" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -25845,7 +25845,7 @@
       </c>
       <c r="F211" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -25877,7 +25877,7 @@
       </c>
       <c r="F212" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -25909,7 +25909,7 @@
       </c>
       <c r="F213" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -25941,7 +25941,7 @@
       </c>
       <c r="F214" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -25973,7 +25973,7 @@
       </c>
       <c r="F215" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -26005,7 +26005,7 @@
       </c>
       <c r="F216" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -26037,7 +26037,7 @@
       </c>
       <c r="F217" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -26069,7 +26069,7 @@
       </c>
       <c r="F218" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -26101,7 +26101,7 @@
       </c>
       <c r="F219" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -26133,7 +26133,7 @@
       </c>
       <c r="F220" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -26165,7 +26165,7 @@
       </c>
       <c r="F221" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -26197,7 +26197,7 @@
       </c>
       <c r="F222" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -26229,7 +26229,7 @@
       </c>
       <c r="F223" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -26261,7 +26261,7 @@
       </c>
       <c r="F224" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -26293,7 +26293,7 @@
       </c>
       <c r="F225" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -26325,7 +26325,7 @@
       </c>
       <c r="F226" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -26357,7 +26357,7 @@
       </c>
       <c r="F227" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -26389,7 +26389,7 @@
       </c>
       <c r="F228" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -26421,7 +26421,7 @@
       </c>
       <c r="F229" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -26453,7 +26453,7 @@
       </c>
       <c r="F230" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -26524,7 +26524,7 @@
       </c>
       <c r="F234" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -26556,7 +26556,7 @@
       </c>
       <c r="F235" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -26588,7 +26588,7 @@
       </c>
       <c r="F236" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -26620,7 +26620,7 @@
       </c>
       <c r="F237" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -26652,7 +26652,7 @@
       </c>
       <c r="F238" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -26684,7 +26684,7 @@
       </c>
       <c r="F239" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -26716,7 +26716,7 @@
       </c>
       <c r="F240" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -26748,7 +26748,7 @@
       </c>
       <c r="F241" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -26780,7 +26780,7 @@
       </c>
       <c r="F242" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -26812,7 +26812,7 @@
       </c>
       <c r="F243" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -26844,7 +26844,7 @@
       </c>
       <c r="F244" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -26876,7 +26876,7 @@
       </c>
       <c r="F245" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -26908,7 +26908,7 @@
       </c>
       <c r="F246" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -26940,7 +26940,7 @@
       </c>
       <c r="F247" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -26972,7 +26972,7 @@
       </c>
       <c r="F248" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -27004,7 +27004,7 @@
       </c>
       <c r="F249" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -27036,7 +27036,7 @@
       </c>
       <c r="F250" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -27068,7 +27068,7 @@
       </c>
       <c r="F251" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -27100,7 +27100,7 @@
       </c>
       <c r="F252" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -27132,7 +27132,7 @@
       </c>
       <c r="F253" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -27164,7 +27164,7 @@
       </c>
       <c r="F254" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -27196,7 +27196,7 @@
       </c>
       <c r="F255" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -27228,7 +27228,7 @@
       </c>
       <c r="F256" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -27260,7 +27260,7 @@
       </c>
       <c r="F257" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -27292,7 +27292,7 @@
       </c>
       <c r="F258" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -27324,7 +27324,7 @@
       </c>
       <c r="F259" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -27356,7 +27356,7 @@
       </c>
       <c r="F260" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -27388,7 +27388,7 @@
       </c>
       <c r="F261" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -27420,7 +27420,7 @@
       </c>
       <c r="F262" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -27452,7 +27452,7 @@
       </c>
       <c r="F263" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -27484,7 +27484,7 @@
       </c>
       <c r="F264" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -27516,7 +27516,7 @@
       </c>
       <c r="F265" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -27548,7 +27548,7 @@
       </c>
       <c r="F266" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -27619,7 +27619,7 @@
       </c>
       <c r="F270" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -27651,7 +27651,7 @@
       </c>
       <c r="F271" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -27683,7 +27683,7 @@
       </c>
       <c r="F272" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -27715,7 +27715,7 @@
       </c>
       <c r="F273" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -27747,7 +27747,7 @@
       </c>
       <c r="F274" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -27779,7 +27779,7 @@
       </c>
       <c r="F275" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -27811,7 +27811,7 @@
       </c>
       <c r="F276" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -27843,7 +27843,7 @@
       </c>
       <c r="F277" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -27875,7 +27875,7 @@
       </c>
       <c r="F278" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -27907,7 +27907,7 @@
       </c>
       <c r="F279" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -27939,7 +27939,7 @@
       </c>
       <c r="F280" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -27971,7 +27971,7 @@
       </c>
       <c r="F281" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -28003,7 +28003,7 @@
       </c>
       <c r="F282" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -28074,7 +28074,7 @@
       </c>
       <c r="F286" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -28106,7 +28106,7 @@
       </c>
       <c r="F287" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -28138,7 +28138,7 @@
       </c>
       <c r="F288" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -28170,7 +28170,7 @@
       </c>
       <c r="F289" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -28202,7 +28202,7 @@
       </c>
       <c r="F290" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -28234,7 +28234,7 @@
       </c>
       <c r="F291" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -28266,7 +28266,7 @@
       </c>
       <c r="F292" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -28298,7 +28298,7 @@
       </c>
       <c r="F293" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -28330,7 +28330,7 @@
       </c>
       <c r="F294" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -28362,7 +28362,7 @@
       </c>
       <c r="F295" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -28394,7 +28394,7 @@
       </c>
       <c r="F296" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -28426,7 +28426,7 @@
       </c>
       <c r="F297" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -28458,7 +28458,7 @@
       </c>
       <c r="F298" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -28490,7 +28490,7 @@
       </c>
       <c r="F299" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -28522,7 +28522,7 @@
       </c>
       <c r="F300" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -28554,7 +28554,7 @@
       </c>
       <c r="F301" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -28586,7 +28586,7 @@
       </c>
       <c r="F302" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -28618,7 +28618,7 @@
       </c>
       <c r="F303" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -28650,7 +28650,7 @@
       </c>
       <c r="F304" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -28682,7 +28682,7 @@
       </c>
       <c r="F305" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -28714,7 +28714,7 @@
       </c>
       <c r="F306" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -28746,7 +28746,7 @@
       </c>
       <c r="F307" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -28778,7 +28778,7 @@
       </c>
       <c r="F308" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -28810,7 +28810,7 @@
       </c>
       <c r="F309" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -28842,7 +28842,7 @@
       </c>
       <c r="F310" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="F311" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -28906,7 +28906,7 @@
       </c>
       <c r="F312" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -28938,7 +28938,7 @@
       </c>
       <c r="F313" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -28970,7 +28970,7 @@
       </c>
       <c r="F314" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -29002,7 +29002,7 @@
       </c>
       <c r="F315" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -29034,7 +29034,7 @@
       </c>
       <c r="F316" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -29066,7 +29066,7 @@
       </c>
       <c r="F317" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -29098,7 +29098,7 @@
       </c>
       <c r="F318" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -29169,7 +29169,7 @@
       </c>
       <c r="F322" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -29201,7 +29201,7 @@
       </c>
       <c r="F323" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -29233,7 +29233,7 @@
       </c>
       <c r="F324" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -29265,7 +29265,7 @@
       </c>
       <c r="F325" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -29297,7 +29297,7 @@
       </c>
       <c r="F326" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -29329,7 +29329,7 @@
       </c>
       <c r="F327" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -29361,7 +29361,7 @@
       </c>
       <c r="F328" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -29393,7 +29393,7 @@
       </c>
       <c r="F329" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -29425,7 +29425,7 @@
       </c>
       <c r="F330" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -29457,7 +29457,7 @@
       </c>
       <c r="F331" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -29489,7 +29489,7 @@
       </c>
       <c r="F332" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -29521,7 +29521,7 @@
       </c>
       <c r="F333" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -29553,7 +29553,7 @@
       </c>
       <c r="F334" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -29585,7 +29585,7 @@
       </c>
       <c r="F335" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -29656,7 +29656,7 @@
       </c>
       <c r="F339" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -29688,7 +29688,7 @@
       </c>
       <c r="F340" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -29720,7 +29720,7 @@
       </c>
       <c r="F341" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -29752,7 +29752,7 @@
       </c>
       <c r="F342" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -29784,7 +29784,7 @@
       </c>
       <c r="F343" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -29816,7 +29816,7 @@
       </c>
       <c r="F344" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -29848,7 +29848,7 @@
       </c>
       <c r="F345" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -29880,7 +29880,7 @@
       </c>
       <c r="F346" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -29951,7 +29951,7 @@
       </c>
       <c r="F350" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -29983,7 +29983,7 @@
       </c>
       <c r="F351" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -30015,7 +30015,7 @@
       </c>
       <c r="F352" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -30047,7 +30047,7 @@
       </c>
       <c r="F353" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -30079,7 +30079,7 @@
       </c>
       <c r="F354" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -30111,7 +30111,7 @@
       </c>
       <c r="F355" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -30143,7 +30143,7 @@
       </c>
       <c r="F356" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -30175,7 +30175,7 @@
       </c>
       <c r="F357" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -30207,7 +30207,7 @@
       </c>
       <c r="F358" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -30239,7 +30239,7 @@
       </c>
       <c r="F359" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -30271,7 +30271,7 @@
       </c>
       <c r="F360" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -30303,7 +30303,7 @@
       </c>
       <c r="F361" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -30374,7 +30374,7 @@
       </c>
       <c r="F365" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -30406,7 +30406,7 @@
       </c>
       <c r="F366" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -30438,7 +30438,7 @@
       </c>
       <c r="F367" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -30470,7 +30470,7 @@
       </c>
       <c r="F368" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -30502,7 +30502,7 @@
       </c>
       <c r="F369" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -30534,7 +30534,7 @@
       </c>
       <c r="F370" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -30566,7 +30566,7 @@
       </c>
       <c r="F371" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -30598,7 +30598,7 @@
       </c>
       <c r="F372" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -30630,7 +30630,7 @@
       </c>
       <c r="F373" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -30662,7 +30662,7 @@
       </c>
       <c r="F374" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -30733,7 +30733,7 @@
       </c>
       <c r="F378" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -30765,7 +30765,7 @@
       </c>
       <c r="F379" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -30797,7 +30797,7 @@
       </c>
       <c r="F380" s="9" t="inlineStr">
         <is>
-          <t>Г_Ж_1_курс_2026-2027_Фэб_фдтио_Фиит.xlsx</t>
+          <t>1_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -30829,7 +30829,7 @@
       </c>
       <c r="F381" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -30861,7 +30861,7 @@
       </c>
       <c r="F382" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -30893,7 +30893,7 @@
       </c>
       <c r="F383" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -30925,7 +30925,7 @@
       </c>
       <c r="F384" s="9" t="inlineStr">
         <is>
-          <t>Г_Ж_1_курс_2026-2027_Фэб_фдтио_Фиит.xlsx</t>
+          <t>1_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -30957,7 +30957,7 @@
       </c>
       <c r="F385" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -30989,7 +30989,7 @@
       </c>
       <c r="F386" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -31021,7 +31021,7 @@
       </c>
       <c r="F387" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -31053,7 +31053,7 @@
       </c>
       <c r="F388" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -31085,7 +31085,7 @@
       </c>
       <c r="F389" s="9" t="inlineStr">
         <is>
-          <t>Г_Ж_1_курс_2026-2027_Фэб_фдтио_Фиит.xlsx</t>
+          <t>1_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -31117,7 +31117,7 @@
       </c>
       <c r="F390" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -31149,7 +31149,7 @@
       </c>
       <c r="F391" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -31181,7 +31181,7 @@
       </c>
       <c r="F392" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -31213,7 +31213,7 @@
       </c>
       <c r="F393" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -31284,7 +31284,7 @@
       </c>
       <c r="F397" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -31316,7 +31316,7 @@
       </c>
       <c r="F398" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -31348,7 +31348,7 @@
       </c>
       <c r="F399" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -31380,7 +31380,7 @@
       </c>
       <c r="F400" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -31412,7 +31412,7 @@
       </c>
       <c r="F401" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -31444,7 +31444,7 @@
       </c>
       <c r="F402" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -31476,7 +31476,7 @@
       </c>
       <c r="F403" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -31508,7 +31508,7 @@
       </c>
       <c r="F404" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -31540,7 +31540,7 @@
       </c>
       <c r="F405" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -31572,7 +31572,7 @@
       </c>
       <c r="F406" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -31604,7 +31604,7 @@
       </c>
       <c r="F407" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -31636,7 +31636,7 @@
       </c>
       <c r="F408" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -31668,7 +31668,7 @@
       </c>
       <c r="F409" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -31700,7 +31700,7 @@
       </c>
       <c r="F410" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -31732,7 +31732,7 @@
       </c>
       <c r="F411" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -31803,7 +31803,7 @@
       </c>
       <c r="F415" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -31835,7 +31835,7 @@
       </c>
       <c r="F416" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -31867,7 +31867,7 @@
       </c>
       <c r="F417" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -31899,7 +31899,7 @@
       </c>
       <c r="F418" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -31931,7 +31931,7 @@
       </c>
       <c r="F419" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -31963,7 +31963,7 @@
       </c>
       <c r="F420" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -31995,7 +31995,7 @@
       </c>
       <c r="F421" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -32027,7 +32027,7 @@
       </c>
       <c r="F422" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -32059,7 +32059,7 @@
       </c>
       <c r="F423" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -32091,7 +32091,7 @@
       </c>
       <c r="F424" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -32123,7 +32123,7 @@
       </c>
       <c r="F425" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -32155,7 +32155,7 @@
       </c>
       <c r="F426" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -32187,7 +32187,7 @@
       </c>
       <c r="F427" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -32219,7 +32219,7 @@
       </c>
       <c r="F428" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -32251,7 +32251,7 @@
       </c>
       <c r="F429" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -32283,7 +32283,7 @@
       </c>
       <c r="F430" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -32315,7 +32315,7 @@
       </c>
       <c r="F431" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -32347,7 +32347,7 @@
       </c>
       <c r="F432" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -32379,7 +32379,7 @@
       </c>
       <c r="F433" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -32450,7 +32450,7 @@
       </c>
       <c r="F437" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -32482,7 +32482,7 @@
       </c>
       <c r="F438" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -32514,7 +32514,7 @@
       </c>
       <c r="F439" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -32546,7 +32546,7 @@
       </c>
       <c r="F440" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -32578,7 +32578,7 @@
       </c>
       <c r="F441" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -32610,7 +32610,7 @@
       </c>
       <c r="F442" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -32642,7 +32642,7 @@
       </c>
       <c r="F443" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -32674,7 +32674,7 @@
       </c>
       <c r="F444" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -32706,7 +32706,7 @@
       </c>
       <c r="F445" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -32777,7 +32777,7 @@
       </c>
       <c r="F449" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -32809,7 +32809,7 @@
       </c>
       <c r="F450" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -32841,7 +32841,7 @@
       </c>
       <c r="F451" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -32873,7 +32873,7 @@
       </c>
       <c r="F452" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -32905,7 +32905,7 @@
       </c>
       <c r="F453" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -32937,7 +32937,7 @@
       </c>
       <c r="F454" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -32969,7 +32969,7 @@
       </c>
       <c r="F455" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -33001,7 +33001,7 @@
       </c>
       <c r="F456" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -33033,7 +33033,7 @@
       </c>
       <c r="F457" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -33065,7 +33065,7 @@
       </c>
       <c r="F458" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -33097,7 +33097,7 @@
       </c>
       <c r="F459" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -33129,7 +33129,7 @@
       </c>
       <c r="F460" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -33161,7 +33161,7 @@
       </c>
       <c r="F461" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -33193,7 +33193,7 @@
       </c>
       <c r="F462" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -33225,7 +33225,7 @@
       </c>
       <c r="F463" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -33257,7 +33257,7 @@
       </c>
       <c r="F464" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -33328,7 +33328,7 @@
       </c>
       <c r="F468" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -33360,7 +33360,7 @@
       </c>
       <c r="F469" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -33392,7 +33392,7 @@
       </c>
       <c r="F470" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -33424,7 +33424,7 @@
       </c>
       <c r="F471" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -33456,7 +33456,7 @@
       </c>
       <c r="F472" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -33488,7 +33488,7 @@
       </c>
       <c r="F473" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -33520,7 +33520,7 @@
       </c>
       <c r="F474" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -33552,7 +33552,7 @@
       </c>
       <c r="F475" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -33584,7 +33584,7 @@
       </c>
       <c r="F476" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -33655,7 +33655,7 @@
       </c>
       <c r="F480" s="9" t="inlineStr">
         <is>
-          <t>МАГИСТРАТУРА_1_КУРС_ПРОФИЛЬНОЕ_НАПР__2026-2027_г_.xlsx</t>
+          <t>magistratura_profil.xlsx</t>
         </is>
       </c>
     </row>
@@ -33726,7 +33726,7 @@
       </c>
       <c r="F484" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -33758,7 +33758,7 @@
       </c>
       <c r="F485" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -33790,7 +33790,7 @@
       </c>
       <c r="F486" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -33861,7 +33861,7 @@
       </c>
       <c r="F490" s="9" t="inlineStr">
         <is>
-          <t>Расписание_магистрантов_2_курс.xlsx</t>
+          <t>magistratura_2kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -33893,7 +33893,7 @@
       </c>
       <c r="F491" s="9" t="inlineStr">
         <is>
-          <t>Расписание_магистрантов_2_курс.xlsx</t>
+          <t>magistratura_2kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -33925,7 +33925,7 @@
       </c>
       <c r="F492" s="9" t="inlineStr">
         <is>
-          <t>МАГИСТРАТУРА_1_КУРС_ПРОФИЛЬНОЕ_НАПР__2026-2027_г_.xlsx</t>
+          <t>magistratura_profil.xlsx</t>
         </is>
       </c>
     </row>
@@ -33996,7 +33996,7 @@
       </c>
       <c r="F496" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -34028,7 +34028,7 @@
       </c>
       <c r="F497" s="9" t="inlineStr">
         <is>
-          <t>Расписание_магистрантов_2_курс.xlsx</t>
+          <t>magistratura_2kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -34060,7 +34060,7 @@
       </c>
       <c r="F498" s="9" t="inlineStr">
         <is>
-          <t>Расписание_магистрантов_2_курс.xlsx</t>
+          <t>magistratura_2kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -34092,7 +34092,7 @@
       </c>
       <c r="F499" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -34163,7 +34163,7 @@
       </c>
       <c r="F503" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -34195,7 +34195,7 @@
       </c>
       <c r="F504" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -34227,7 +34227,7 @@
       </c>
       <c r="F505" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -34259,7 +34259,7 @@
       </c>
       <c r="F506" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -34291,7 +34291,7 @@
       </c>
       <c r="F507" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -34383,7 +34383,7 @@
       </c>
       <c r="F517" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -34454,7 +34454,7 @@
       </c>
       <c r="F521" s="9" t="inlineStr">
         <is>
-          <t>Расписание_магистрантов_2_курс.xlsx</t>
+          <t>magistratura_2kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -34486,7 +34486,7 @@
       </c>
       <c r="F522" s="9" t="inlineStr">
         <is>
-          <t>МАГИСТРАТУРА_1_КУРС_ПРОФИЛЬНОЕ_НАПР__2026-2027_г_.xlsx</t>
+          <t>magistratura_profil.xlsx</t>
         </is>
       </c>
     </row>
@@ -34557,7 +34557,7 @@
       </c>
       <c r="F526" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -34589,7 +34589,7 @@
       </c>
       <c r="F527" s="9" t="inlineStr">
         <is>
-          <t>Расписание_магистрантов_2_курс.xlsx</t>
+          <t>magistratura_2kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -34621,7 +34621,7 @@
       </c>
       <c r="F528" s="9" t="inlineStr">
         <is>
-          <t>Расписание_магистрантов_2_курс.xlsx</t>
+          <t>magistratura_2kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -34653,7 +34653,7 @@
       </c>
       <c r="F529" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -34724,7 +34724,7 @@
       </c>
       <c r="F533" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -34756,7 +34756,7 @@
       </c>
       <c r="F534" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -34788,7 +34788,7 @@
       </c>
       <c r="F535" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -34859,7 +34859,7 @@
       </c>
       <c r="F539" s="9" t="inlineStr">
         <is>
-          <t>МАГИСТРАТУРА_1_КУРС_ПРОФИЛЬНОЕ_НАПР__2026-2027_г_.xlsx</t>
+          <t>magistratura_profil.xlsx</t>
         </is>
       </c>
     </row>
@@ -34930,7 +34930,7 @@
       </c>
       <c r="F543" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -34962,7 +34962,7 @@
       </c>
       <c r="F544" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -34994,7 +34994,7 @@
       </c>
       <c r="F545" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -35026,7 +35026,7 @@
       </c>
       <c r="F546" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -35058,7 +35058,7 @@
       </c>
       <c r="F547" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -35129,7 +35129,7 @@
       </c>
       <c r="F551" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -35161,7 +35161,7 @@
       </c>
       <c r="F552" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -35193,7 +35193,7 @@
       </c>
       <c r="F553" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -35264,7 +35264,7 @@
       </c>
       <c r="F557" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -35296,7 +35296,7 @@
       </c>
       <c r="F558" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -35367,7 +35367,7 @@
       </c>
       <c r="F562" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -35399,7 +35399,7 @@
       </c>
       <c r="F563" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -35431,7 +35431,7 @@
       </c>
       <c r="F564" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -35463,7 +35463,7 @@
       </c>
       <c r="F565" s="9" t="inlineStr">
         <is>
-          <t>4_курс_расписание_2026-2027_г_10_09.xlsx</t>
+          <t>4_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -35495,7 +35495,7 @@
       </c>
       <c r="F566" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -35566,7 +35566,7 @@
       </c>
       <c r="F570" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -35598,7 +35598,7 @@
       </c>
       <c r="F571" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -35630,7 +35630,7 @@
       </c>
       <c r="F572" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -35662,7 +35662,7 @@
       </c>
       <c r="F573" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -35694,7 +35694,7 @@
       </c>
       <c r="F574" s="9" t="inlineStr">
         <is>
-          <t>2_курс_ФИиИТ_ФИиИС_Расписание_1_академического_периода_2026-2027уч_года.xlsx</t>
+          <t>2_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -35765,7 +35765,7 @@
       </c>
       <c r="F578" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>
@@ -35797,7 +35797,7 @@
       </c>
       <c r="F579" s="9" t="inlineStr">
         <is>
-          <t>3_курс_2026-2027.xlsx</t>
+          <t>3_kurs.xlsx</t>
         </is>
       </c>
     </row>

--- a/dist/Кафедра_ИС_занятия_преподавателей_2026-2027.xlsx
+++ b/dist/Кафедра_ИС_занятия_преподавателей_2026-2027.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Все занятия" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="По преподавателям" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Сводка" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Все занятия" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="По преподавателям" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Все занятия'!$A$1:$H$444</definedName>
